--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="113">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,58 +40,64 @@
     <t>Source</t>
   </si>
   <si>
-    <t>edrelectronics.com</t>
-  </si>
-  <si>
-    <t>Blog</t>
-  </si>
-  <si>
-    <t>Service Area | EDR Electronics | Arlington Heights,IL</t>
-  </si>
-  <si>
-    <t>FAQ -edrelectronics.com</t>
-  </si>
-  <si>
-    <t>edrelectronics</t>
-  </si>
-  <si>
-    <t>Geo Pages -edrelectronics.com</t>
-  </si>
-  <si>
-    <t>Machinery Repair Services for Industrial | EDR Electronics Inc.</t>
-  </si>
-  <si>
-    <t>Automation Control Services | EDR Electronics | Arlington Heights,IL</t>
-  </si>
-  <si>
-    <t>#1Best JDM Imports In Colorado- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>JDM Sport Classics - Classic Japanese Car Importers</t>
-  </si>
-  <si>
-    <t>2000 HondaCivicG - JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>Hondacivic-ferio 1993 - JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>Toyota Supra inColorado- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>#1Best JDM Imports In North Carolina- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>Nissan Skyline in Colorado- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>#1Best JDM Imports In New Jersey- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>#1Best JDM Imports In Illinois- JDM Sport Classics</t>
-  </si>
-  <si>
-    <t>#1Best JDM Imports In Mississippi- JDM Sport Classics</t>
+    <t>community（英语单词）_百度百科</t>
+  </si>
+  <si>
+    <t>Community-Wikipedia</t>
+  </si>
+  <si>
+    <t>COMMUNITY中文 (简体)翻译：剑桥词典</t>
+  </si>
+  <si>
+    <t>community是什么意思_community的翻译_音标_读音_用法_例句_爱词 …</t>
+  </si>
+  <si>
+    <t>COMMUNITY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>浅谈词汇多重意义之三："community" 未必是“社区” - 知乎</t>
+  </si>
+  <si>
+    <t>COMMUNITY释义 | 柯林斯英语词典</t>
+  </si>
+  <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>community- 搜索 词典</t>
+  </si>
+  <si>
+    <t>Honda CivicFamily: Models &amp; Price | Honda</t>
+  </si>
+  <si>
+    <t>Honda Civic- Wikipedia</t>
+  </si>
+  <si>
+    <t>2026CivicSedan - Fun &amp; Sporty Compact w/ Hybrid Option</t>
+  </si>
+  <si>
+    <t>Used HondaCivicfor Sale inEscondido,CA- Autotrader</t>
+  </si>
+  <si>
+    <t>New HondaCivicfor Sale inEscondido,CA</t>
+  </si>
+  <si>
+    <t>New and Used Honda DealerEscondido CA- Honda ofEscondido</t>
+  </si>
+  <si>
+    <t>New HondaCivicfor Sale inEscondido,CA- Autotrader</t>
+  </si>
+  <si>
+    <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
+  </si>
+  <si>
+    <t>Used HondaCivicnearEscondido,CAfor sale - CarMax</t>
+  </si>
+  <si>
+    <t>2026Honda CivicPrice, Reviews, Pictures &amp; More | Kelley Blue Book</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -103,85 +109,85 @@
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
+    <t>Nextdoor - Discover yourneighbourhood</t>
+  </si>
+  <si>
+    <t>Login - Nextdoor</t>
+  </si>
+  <si>
+    <t>The Neighbourhood-Wikipedia</t>
+  </si>
+  <si>
+    <t>The Neighbourhood-YouTube</t>
+  </si>
+  <si>
+    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
+  </si>
+  <si>
     <t>TheNeighbourhood- Wourld Tour</t>
   </si>
   <si>
-    <t>The Neighbourhood-Wikipedia</t>
-  </si>
-  <si>
-    <t>The Neighbourhood-YouTube</t>
-  </si>
-  <si>
-    <t>Nextdoor - Discover yourneighbourhood</t>
-  </si>
-  <si>
     <t>TheNeighbourhood- Sweater Weather (Official Video)</t>
   </si>
   <si>
-    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
+    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
   </si>
   <si>
     <t>The Residents Official Site</t>
   </si>
   <si>
-    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
-  </si>
-  <si>
     <t>The Residents-Wikipedia</t>
   </si>
   <si>
-    <t>MichiganResidentsDatabase Search</t>
-  </si>
-  <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Residents– COUNTY OF LOS ANGELES</t>
+  </si>
+  <si>
+    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
+  </si>
+  <si>
     <t>Live &amp; Preserved - TheResidents</t>
   </si>
   <si>
-    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
-  </si>
-  <si>
-    <t>The Residents - Topic-YouTube</t>
-  </si>
-  <si>
-    <t>WardTransport &amp; Logistics | LTL Freight Services</t>
-  </si>
-  <si>
-    <t>WARDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Ward-Wikipedia</t>
-  </si>
-  <si>
-    <t>WARD| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>WardApp - Apps on Google Play</t>
-  </si>
-  <si>
-    <t>Montgomery Ward|Buy Now Pay LaterCredit</t>
-  </si>
-  <si>
-    <t>What is aWard? The 'Bridgerton' Term Explained - Parade</t>
-  </si>
-  <si>
-    <t>Ward- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>Ward (United States) -Wikipedia</t>
-  </si>
-  <si>
-    <t>WARDDefinition &amp; Meaning |Dictionary.com</t>
+    <t>Residents- definition ofresidentsby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>Scores &amp; Fixtures - Football - BBC Sport</t>
+  </si>
+  <si>
+    <t>Football - latest news today, results &amp; video highlights - BBC Sport</t>
+  </si>
+  <si>
+    <t>Premier League - Scores &amp; Fixtures - Football - BBC Sport</t>
+  </si>
+  <si>
+    <t>Championship - Scores &amp; Fixtures - Football - BBC Sport</t>
+  </si>
+  <si>
+    <t>Premier League Football - Latest news, results, stats &amp; transfers - BBC</t>
+  </si>
+  <si>
+    <t>Rugby Union - latest news today, results &amp; video - BBC Sport</t>
+  </si>
+  <si>
+    <t>Cricket – Ashes, Test, T20 &amp; ODI news, scores &amp; results - BBC</t>
+  </si>
+  <si>
+    <t>Scottish Premiership - Scores &amp; Fixtures - Football - BBC Sport</t>
+  </si>
+  <si>
+    <t>Irish - Scores &amp; Fixtures - Football - BBC Sport</t>
+  </si>
+  <si>
+    <t>England - Scores &amp; Fixtures - Football - BBC Sport</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -190,151 +196,160 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a80764835c2913f122478e66d337a550cb51b5c4bc1c292baafec8fd5a2d3c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly9lZHJlbGVjdHJvbmljcy5jb20vaW5kZXguaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2e27d229c94b48a822ddf2638413085b0500d8fc0dbfab554582033940b81fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL2Jsb2c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0f7d7fef60edac61ceae4031eb814af2b5f0fab296634b32d37c2669c02d034JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL3NlcnZpY2UtYXJlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21891dc04330ab815b583bc009e70d2e7e530de586ef4ebaa1a3551691105d22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL2ZhcQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed62d5684685564a5d6a8676fc6fff69265c2258a9d8368321fdbb4e056c9c72JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL2ZlZWQvcnNzMg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf4c0065bd52ad4a678d0b3c51c0e4b1f076119b7ecc05d60bd586bbd13a1ea8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL2dlby1wYWdlcy9lbGstZ3JvdmUtdmlsbGFnZS1pbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81a53e4e5e87390812cbb96d966a92d2412c5b72488473f14fecfebc4cd44881JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL21hY2hpbmVyeS1yZXBhaXItc2VydmljZXMtZm9yLWluZHVzdHJpYWwtZXF1aXBtZW50LWluLWVsay1ncm92ZS12aWxsYWdlLWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08854ba8e0f85a1022558edd60c0d7ca81185bd1101bf3b5c0fd77ced80953d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=273716c9-1226-6f58-03d0-012813ce6e71&amp;u=a1aHR0cHM6Ly93d3cuZWRyZWxlY3Ryb25pY3MuY29tL2NvbnRhY3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee5b444ef3f84945ee2b53885cfd874ca47ef9b7e33dc6f5f0cd0282807ca935JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8xLWJlc3QtamRtLWltcG9ydHMtaW4tY29sb3JhZG8v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f5edac4396fd04858d978869638c47fb13c090afce9bf76396f8cc579790c39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d88e28b713d3398845e106d86719f4780a0908fde114a890c59a0d40155b3f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS9pbnZlbnRvcnkvMjAwMC1ob25kYS1jaXZpYy1nLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24593764d9192357c329f1f3e4720c6a75deeba8d1e9edd5c230ae3ce7f3c88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS9pbnZlbnRvcnkvMTk5My1ob25kYS1jaXZpYy1mZXJpby8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98185868bba99d95886dd98e59994ed070c1ac59ccc663720e6c5e1a397e01e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS90b3lvdGEtc3VwcmEtaW4tY29sb3JhZG8v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e36502a8b5a32df8de67808a201124ed1c2aec91ff56c605334ada9a55d1469JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8xLWJlc3QtamRtLWltcG9ydHMtaW4tbm9ydGgtY2Fyb2xpbmEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=776321657aad829e4b515bb9fd51039ccead1384297490f73e32fb2295e5f1d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS9uaXNzYW4tc2t5bGluZS1pbi1jb2xvcmFkby8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c17fa6d741386ea800a879827f5c6974fbff98c4097ae19c27346f1daf0b0677JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8xLWJlc3QtamRtLWltcG9ydHMtaW4tbmV3LWplcnNleS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f69553c22fc96ab3ca1e45099e564cf1b3f16768ff7743261214dfdbfa810ed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8xLWJlc3QtamRtLWltcG9ydHMtaW4taWxsaW5vaXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06ba0039c47e65f0554e4dbd5d82f06b49f9fdf5ed5119c753cf7dd9016b8301JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=156bb91c-62bf-6f92-3b0c-aefd634e6e65&amp;u=a1aHR0cHM6Ly9qZG1zcG9ydGNsYXNzaWNzLmNvbS8xLWJlc3QtamRtLWltcG9ydHMtaW4tbWlzc2lzc2lwcGkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b1ff4c60df77f9310998386cbcca48454d3f51a818b92c843897c64c1d44967JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=907d81ad4cee089d0df8e4ba2a247abae2a8c6f65fb407e3809b4f68ae3ea2f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aad225ccf3a977a4a4a49a5f672b6dbbea7f3fcd6b2e0658617384321630f752JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3164930fe065ef6bd521e0d950a446ae5dbc5cb7b4fb6ff734bfc4ad720b6597JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1a8c5afc3c53c722ac16797bf00e95f2a18020353bd137f50714ea1046a462eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f75f2675f77e57abafeed8aefb5d576a8f08616e8ec1c97b674ab2fc7b7f9ae5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09868152caa84d4891feff222f7d00f846d4b18bba812f62891a2ce2995638f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7068c72fdda7b544eecdda3304d894a01e8bf035bdbd8e60858a576652170d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9R0Nkd0toVHROTnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=885dab08350327586faa09e9fb3ccbd0ed6cc92691baec353a5d405b5f42797cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8213fd9ecd1e7641779cd413c98ab1404b8f8b43efd98d80bd598178eb36c5e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12ad742a-fe33-6373-1f29-63cbffa462f5&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f805389ab91dd3498d7d560c2611e7488e45d5f65b25bc1320cfcfe463e7ca0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=815aea4f9950789035acde2214d81768f024366a6ceae69dad58d9f1af89ad9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9Mjc3NTQ0NTg3YzgxNmJhODBmY2Y1M2I5N2Q5OTZhOTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc129713bd63e13d3c801a47033a69bb0c69431dfd262f3a76b59dde3f4ed7a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8cb5a97a25d3e5e2d60cb902c5ab4133be547b3c6ee488a267a29ce542868121JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cubWljaGlnYW5yZXNpZGVudGRhdGFiYXNlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5eb45a5c9de12189cfffca26da64e6b62d68482961c597ed05d3e88172ca9ed1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0f9e7e4328bf730c6eacb012449099e5d27e3b096f6a047beecc775f7102441JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f491feaca0bec746cb0abde0d99550479ae2be20f7cfe9faf659b8a4f72e63fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1cf4232ba900f88ded248a67dd1c29dbb7a1921b9f4a5aad18bc8bebf601925JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0f53a264a0467ed8a96d1320b6c26b82231219ee4318b598d415b629ca31c49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3bc3847f5c86ed3b81041b460d59b80fce530d43c9873e819a14da1977d3097JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27754458-7c81-6ba8-0fcf-53b97d996a94&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ3IyeGRUWXJZLVEwMlBWZWJyVGRnaVE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c37bbce9b70834f43cf69109b08da15895b86960cea42c9210dd4d2052c18ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly93d3cud2FyZHRsYy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c28f9501890c507a4551afe6e5dd647ab052c9a7f7cdd4481c14da8f9cd53727JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dhcmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8359c3216ecc23fbf3b663fac73db77a56d364f56cf064cc7e4a316e3d08f95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2FyZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ff8840ec89911c67215c08e7174809869279fa8e160446014f217b7b1d58f7cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3dhcmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d5f35ab28a719ef6ab8b77006d5663f95384e679bc437dd98d19e3d9ea804bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS50ZWNocmNzLndhcmRhcHAmaGw9ZW4tVVM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c17ea43c0f9ab4c113bb76cb7c9b0657f50953a5f740cdd73bf5d8af5803475JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly93d3cud2FyZHMuY29tLz9tc29ja2lkPTIwNTgxNTZhNjhmYjZiNjcyMzZmMDI4YjY5NTg2YTY0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e49ff612e6519f0543e6d90b375b046a5adee99474b2d2b0062c6224a0f6b06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly9wYXJhZGUuY29tL3R2L3doYXQtaXMtYS13YXJkLXRoZS1icmlkZ2VydG9uLXRlcm0tZXhwbGFpbmVk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf9cc1b19588f72ddfb92ce38d7b51aacea1648fcff866a30bfe721fc2c8833eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS93YXJk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34a6d32ad98f220bbac724f5d62d323cdf26f1be46cd29d2b12752f2ab6c1f47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2FyZF8oVW5pdGVkX1N0YXRlcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=414ae16748f1f07d0c8733269d0663e755c5aea6f74f3a134ad2b74b87d8d6daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2058156a-68fb-6b67-236f-028b69586a64&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3dhcmQ&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07c5e372adef6f4922049baed7860050b9ab6c4871da10ffaee8969c61af40d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9jb21tdW5pdHkvOTM3MjM0OQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=530e019fcd98e2eb4640c81aced86158b5f2c02be8f16e038b1a284edbfb4f57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1fca2f37d1c0dd32c549bdcaf55093070465f9e268602c47bfdc43e4e87e3e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9jb21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aafcebdeb81fbcb407d1d780729234220180c5d5d0120e49902df411fef71c1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1jb21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be33d9958b6fc40eb099f120696b12b40793260489b03047fa3ee7b398b6dc24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=767849f19f0a4a085ddd9810707df55a2bc73862ed4e3e1fae47d87b5df2dd64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=716ea6e472ed86e9538089d155eb173b383e83eee5e09c937088fce311c924a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly96aHVhbmxhbi56aGlodS5jb20vcC80MDIxODA0MTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7db61797e5da9c48c4f6a327467ceae92f1e9878f5f00834233f35d32f3c07b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9jb21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7d6566ce5f2efeb753643196cf370d07b0082d88f5a237548a020a773d5b0adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=702ff853837d75916580a1a336a781206e90e2b31db5a870c637fac297222955JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9nbG9iYWwuYmluZy5jb20vZGljdC9zZWFyY2g_cT1jb21tdW5pdHkmRk9STT1CRFZTUDYmY2M9Y24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45f98c2cecdfc9fe82b125745a639fda063749b1b4738411418a3c45003260e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=459a2320c4868aee44c02e6c816fe01de0601da82e1e4acf05036a788c4d0f4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0acf22f5d0a9edd8f4f0fed29073cfbc039d13fdbd55d39dc9a433d3c66499edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d03d4c26ab01e3730aa8736b94d84bc1d54dc4a7761778d1ddd3abe2671a691JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9lc2NvbmRpZG8tY2E_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75e8b44677e604ae567afe4cbbdeee807b4be1478648512bdc906ab95a78935aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuaG9uZGFvZmVzY29uZGlkby5jb20vbmV3LXZlaGljbGVzL2NpdmljLXNlZGFuLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4b5e7a91539f6e8a9070fb3eb9897ab4009845c80f34dffa48d1942563d0644JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuaG9uZGFvZmVzY29uZGlkby5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0db2b7a342fa15a5bb7ebedab4332043d1c8a35735b1c73da576b418d7cc1a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9uZXctY2Fycy9ob25kYS9jaXZpYy9lc2NvbmRpZG8tY2E_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8010d1112fd85216c7577af4ed6c620ad37ba82b877b087f00e6550f7e454f26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a288e7851bcaf1694fd4dc48625a4dd38ba3d960b4fb52b9b95c6ef362c6fceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuY2FybWF4LmNvbS9jYXJzL2hvbmRhL2NpdmljP2xvY2F0aW9uPWVzY29uZGlkbytjYSZtc29ja2lkPTFlNjA2ZGYyMzUyZTYzMDMwNjNiN2ExMzM0ZDE2MjEx&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e928f316fa10db00119f1cd17870c9458a2ab6730ead1cb6bf791ad9401c4b20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e57795932479f8b57108726e500fa9c1760c2e8f1243b6042cc362c03dfac659JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2325e62e1e33f561bfd232334e17c5a9ae5209b213fb80e8570389fd31e90f99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11a6530caae8c2f43b01f6b4a0abb1efc4dd3b04dd688e45a7b9aca90cedd1c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f959bdc42a8c9e48350c871ab36c0ab697db017fdd882815a942040dbbade35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3904acca6f83214d0ec9484a4d782f127b667d10eeb207510f35621b2a555f0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20vbG9naW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a43d7edf0e08044c3ad961d05a278f81e1da7ae8020552bb4c9e6b96323c949JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX05laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d73cf733e17bcb7ad784a1ecda0d06b75b622fce90e83e470b40c55e351992eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecee449cb907baccc2552b797be2614c94b7844806b8089492ac1db5704a3f7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc736d65015dd835b3de9d0151ac79dac621dcd0e06d401bb99a8a1fde2e97f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=836616998f4d8e76524355b672375a6164c4b83687e6a228864a152dc0e6295eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1HQ2R3S2hUdE5Odw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=457dc8c7b17c24b32cd0be6762126c82021b43ccd027be98e49c6bfebdb9b36eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MWE3NmY1NWU2ZWMwNjdkMjEyNzhlMmJmNmY5NjY2NjI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8dc2e36d1eab22ee146b6f41eab89b19f60e53f57108d34841ff3bde48cfebaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19ec86ab9d7b3f1340083a0707854f8eaa2cac8bb92213df3f1d9f84216033baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b5da55df008ac49c290d4ea46169f1e2f0ab8137e59637ecdbca58f740f7a7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb8dca24adb9b0a79d98e2394f5ef59dce3ac9c7835da10633c76e545e15e31aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9sYWNvdW50eS5nb3YvcmVzaWRlbnRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39c37090d1afa7df144c019735e709db69dc41e90889073649defe4fc1c48576JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=403799c010bb81bb216f380e7c59c5705c1c89e9fcd667b3f4c5c4bde4901164JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f16d91aed198cca04fd113d2bffd0260fbc955b14494686a51a81b3851f73d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca4df5116d2ddb7b9acc7fceea53a694f60bdb5681fa8358e1294e93aa416395JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be6ea7ecd02123ea9edd6cf083a61fc8df57dccaf0850b952fe816906e1ec498JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7996d8292a81858a627fc7d5abfcba95639670bce09e6716caf9ff8c4453d40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd5a69d180192451fc074d2622cef56da649dc26ca3bf5ba1423515fefe28903JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=756ffb1f9cf31aa2fff28fa4d84ea5106bf0d9490a2104718fca3af428b7009dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3ByZW1pZXItbGVhZ3VlL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cd165f28a2391b60295a0254b5a00055728a510642a374018d0f04a80dc5fd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL2NoYW1waW9uc2hpcC9zY29yZXMtZml4dHVyZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f6dad3e8461218a7af3c237b0c0b207ce32ae2af17cd47a9526d278314d94ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3ByZW1pZXItbGVhZ3Vl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae56f9d6cbbf9126d3d41b29f1ee42dd603595c637fca1c08a0cefa3b06cb114JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3J1Z2J5LXVuaW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e949d802f3ef8cf398c6845a64ec146c1b3911c49a75a9e77e22f7c34a566418JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2NyaWNrZXQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ef0f1b3ceb4482fddb9b79ee971df3f98796784edf314dd3bed2a1b20066822JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3R0aXNoLXByZW1pZXJzaGlwL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44f334d83a24df1e564a5b01e342d480ce48a1bfd0806708133fc14b671c1ab8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL2lyaXNoL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99d5ce89e56a71def639ab660bcd46aaa4bff723f3cc17ff9d6393216c618461JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3RlYW1zL2VuZ2xhbmQvc2NvcmVzLWZpeHR1cmVz&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Green Point</t>
   </si>
   <si>
     <t>Bing</t>
@@ -682,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -716,19 +731,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -736,19 +751,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -756,19 +771,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -776,19 +791,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -796,19 +811,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -816,19 +831,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -836,19 +851,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -856,19 +871,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -876,19 +891,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -896,19 +911,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -916,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -936,19 +951,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -956,19 +971,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -976,19 +991,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -996,19 +1011,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1016,19 +1031,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1036,19 +1051,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1056,19 +1071,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1076,19 +1091,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1096,19 +1111,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H21" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1116,19 +1131,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1136,19 +1151,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1156,19 +1171,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1176,19 +1191,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1196,19 +1211,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H26" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1216,19 +1231,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H27" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1236,19 +1251,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H28" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1256,19 +1271,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H29" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1276,19 +1291,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1296,19 +1311,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H31" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,19 +1331,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1336,19 +1351,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1356,19 +1371,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1376,19 +1391,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1396,19 +1411,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1416,19 +1431,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H37" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1436,19 +1451,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1456,19 +1471,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1476,19 +1491,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1496,19 +1511,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H41" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1516,19 +1531,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H42" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1536,19 +1551,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H43" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1556,19 +1571,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G44" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H44" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1576,19 +1591,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G45" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H45" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1596,19 +1611,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H46" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1616,19 +1631,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G47" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H47" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1636,19 +1651,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H48" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1656,19 +1671,59 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" t="s">
+        <v>111</v>
+      </c>
+      <c r="H49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
         <v>56</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" t="s">
+        <v>111</v>
+      </c>
+      <c r="H50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
         <v>57</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G49" t="s">
-        <v>106</v>
-      </c>
-      <c r="H49" t="s">
-        <v>107</v>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1721,6 +1776,8 @@
     <hyperlink ref="F47" r:id="rId46"/>
     <hyperlink ref="F48" r:id="rId47"/>
     <hyperlink ref="F49" r:id="rId48"/>
+    <hyperlink ref="F50" r:id="rId49"/>
+    <hyperlink ref="F51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
-    <t>community（英语单词）_百度百科</t>
+    <t>Community Information-West Bloomfield Township,Michigan</t>
+  </si>
+  <si>
+    <t>Official Website ofWest Bloomfield Township,MI</t>
   </si>
   <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>COMMUNITY中文 (简体)翻译：剑桥词典</t>
-  </si>
-  <si>
-    <t>community是什么意思_community的翻译_音标_读音_用法_例句_爱词 …</t>
-  </si>
-  <si>
-    <t>COMMUNITY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>浅谈词汇多重意义之三："community" 未必是“社区” - 知乎</t>
-  </si>
-  <si>
-    <t>COMMUNITY释义 | 柯林斯英语词典</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>community- 搜索 词典</t>
+    <t>Home - Bloomfield Township</t>
+  </si>
+  <si>
+    <t>West Bloomfield Twp,MI- Facebook</t>
+  </si>
+  <si>
+    <t>Home - WB Parks</t>
+  </si>
+  <si>
+    <t>West Bloomfield Township,Michigan-Wikipedia</t>
+  </si>
+  <si>
+    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
+  </si>
+  <si>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
@@ -79,27 +79,27 @@
     <t>2026CivicSedan - Fun &amp; Sporty Compact w/ Hybrid Option</t>
   </si>
   <si>
-    <t>Used HondaCivicfor Sale inEscondido,CA- Autotrader</t>
-  </si>
-  <si>
-    <t>New HondaCivicfor Sale inEscondido,CA</t>
-  </si>
-  <si>
-    <t>New and Used Honda DealerEscondido CA- Honda ofEscondido</t>
-  </si>
-  <si>
-    <t>New HondaCivicfor Sale inEscondido,CA- Autotrader</t>
-  </si>
-  <si>
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
-    <t>Used HondaCivicnearEscondido,CAfor sale - CarMax</t>
+    <t>Honda Civic For Sale- Carsforsale.com®</t>
+  </si>
+  <si>
+    <t>HondaCivic(eleventh generation) - Wikipedia</t>
   </si>
   <si>
     <t>2026Honda CivicPrice, Reviews, Pictures &amp; More | Kelley Blue Book</t>
   </si>
   <si>
+    <t>2026Honda CivicReview, Pricing, &amp; Pictures | U.S. News</t>
+  </si>
+  <si>
+    <t>Honda Civic: Prices, Specs &amp; Features by Year | Cars.com</t>
+  </si>
+  <si>
+    <t>Used HondaCivicfor Sale Near Me - Autotrader</t>
+  </si>
+  <si>
     <t>Nextdoor</t>
   </si>
   <si>
@@ -109,85 +109,85 @@
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
+    <t>TheNeighbourhood- Wourld Tour</t>
+  </si>
+  <si>
+    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
+  </si>
+  <si>
     <t>Nextdoor - Discover yourneighbourhood</t>
   </si>
   <si>
+    <t>The Neighbourhood-Wikipedia</t>
+  </si>
+  <si>
     <t>Login - Nextdoor</t>
   </si>
   <si>
-    <t>The Neighbourhood-Wikipedia</t>
+    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
   </si>
   <si>
     <t>The Neighbourhood-YouTube</t>
   </si>
   <si>
-    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
-  </si>
-  <si>
-    <t>TheNeighbourhood- Wourld Tour</t>
-  </si>
-  <si>
-    <t>TheNeighbourhood- Sweater Weather (Official Video)</t>
+    <t>Reddit - Dive into anything</t>
+  </si>
+  <si>
+    <t>News - Reddit</t>
+  </si>
+  <si>
+    <t>What WalMart still sells guns???? - Northeastshooters.com Forums</t>
+  </si>
+  <si>
+    <t>Walmart Ruger 10/22 vs. Gunshop Ruger 10/22</t>
+  </si>
+  <si>
+    <t>r/GamingLeaksAndRumours | Central hub for ALL gaming leaks</t>
+  </si>
+  <si>
+    <t>AITAH - Reddit</t>
+  </si>
+  <si>
+    <t>r/wallstreetbets - Reddit</t>
+  </si>
+  <si>
+    <t>LegoLeak - Reddit</t>
+  </si>
+  <si>
+    <t>r/funny - Reddit</t>
+  </si>
+  <si>
+    <t>reddit</t>
+  </si>
+  <si>
+    <t>The Residents Official Site</t>
   </si>
   <si>
     <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
   </si>
   <si>
-    <t>The Residents Official Site</t>
-  </si>
-  <si>
     <t>The Residents-Wikipedia</t>
   </si>
   <si>
+    <t>MichiganResidentsDatabase Search</t>
+  </si>
+  <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Residents– COUNTY OF LOS ANGELES</t>
+    <t>Live &amp; Preserved - TheResidents</t>
+  </si>
+  <si>
+    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>RESIDENT| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
     <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
-    <t>Live &amp; Preserved - TheResidents</t>
-  </si>
-  <si>
-    <t>Residents- definition ofresidentsby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Scores &amp; Fixtures - Football - BBC Sport</t>
-  </si>
-  <si>
-    <t>Football - latest news today, results &amp; video highlights - BBC Sport</t>
-  </si>
-  <si>
-    <t>Premier League - Scores &amp; Fixtures - Football - BBC Sport</t>
-  </si>
-  <si>
-    <t>Championship - Scores &amp; Fixtures - Football - BBC Sport</t>
-  </si>
-  <si>
-    <t>Premier League Football - Latest news, results, stats &amp; transfers - BBC</t>
-  </si>
-  <si>
-    <t>Rugby Union - latest news today, results &amp; video - BBC Sport</t>
-  </si>
-  <si>
-    <t>Cricket – Ashes, Test, T20 &amp; ODI news, scores &amp; results - BBC</t>
-  </si>
-  <si>
-    <t>Scottish Premiership - Scores &amp; Fixtures - Football - BBC Sport</t>
-  </si>
-  <si>
-    <t>Irish - Scores &amp; Fixtures - Football - BBC Sport</t>
-  </si>
-  <si>
-    <t>England - Scores &amp; Fixtures - Football - BBC Sport</t>
+    <t>The Residents - Topic-YouTube</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -196,160 +196,157 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07c5e372adef6f4922049baed7860050b9ab6c4871da10ffaee8969c61af40d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9jb21tdW5pdHkvOTM3MjM0OQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=530e019fcd98e2eb4640c81aced86158b5f2c02be8f16e038b1a284edbfb4f57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1fca2f37d1c0dd32c549bdcaf55093070465f9e268602c47bfdc43e4e87e3e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aafcebdeb81fbcb407d1d780729234220180c5d5d0120e49902df411fef71c1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be33d9958b6fc40eb099f120696b12b40793260489b03047fa3ee7b398b6dc24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=767849f19f0a4a085ddd9810707df55a2bc73862ed4e3e1fae47d87b5df2dd64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=716ea6e472ed86e9538089d155eb173b383e83eee5e09c937088fce311c924a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly96aHVhbmxhbi56aGlodS5jb20vcC80MDIxODA0MTE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7db61797e5da9c48c4f6a327467ceae92f1e9878f5f00834233f35d32f3c07b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7d6566ce5f2efeb753643196cf370d07b0082d88f5a237548a020a773d5b0adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=702ff853837d75916580a1a336a781206e90e2b31db5a870c637fac297222955JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fee8536-9213-6d6a-39f9-92d793d76c55&amp;u=a1aHR0cHM6Ly9nbG9iYWwuYmluZy5jb20vZGljdC9zZWFyY2g_cT1jb21tdW5pdHkmRk9STT1CRFZTUDYmY2M9Y24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45f98c2cecdfc9fe82b125745a639fda063749b1b4738411418a3c45003260e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=459a2320c4868aee44c02e6c816fe01de0601da82e1e4acf05036a788c4d0f4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0acf22f5d0a9edd8f4f0fed29073cfbc039d13fdbd55d39dc9a433d3c66499edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d03d4c26ab01e3730aa8736b94d84bc1d54dc4a7761778d1ddd3abe2671a691JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9lc2NvbmRpZG8tY2E_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75e8b44677e604ae567afe4cbbdeee807b4be1478648512bdc906ab95a78935aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuaG9uZGFvZmVzY29uZGlkby5jb20vbmV3LXZlaGljbGVzL2NpdmljLXNlZGFuLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4b5e7a91539f6e8a9070fb3eb9897ab4009845c80f34dffa48d1942563d0644JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuaG9uZGFvZmVzY29uZGlkby5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0db2b7a342fa15a5bb7ebedab4332043d1c8a35735b1c73da576b418d7cc1a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9uZXctY2Fycy9ob25kYS9jaXZpYy9lc2NvbmRpZG8tY2E_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8010d1112fd85216c7577af4ed6c620ad37ba82b877b087f00e6550f7e454f26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a288e7851bcaf1694fd4dc48625a4dd38ba3d960b4fb52b9b95c6ef362c6fceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cuY2FybWF4LmNvbS9jYXJzL2hvbmRhL2NpdmljP2xvY2F0aW9uPWVzY29uZGlkbytjYSZtc29ja2lkPTFlNjA2ZGYyMzUyZTYzMDMwNjNiN2ExMzM0ZDE2MjEx&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e928f316fa10db00119f1cd17870c9458a2ab6730ead1cb6bf791ad9401c4b20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e606df2-352e-6303-063b-7a1334d16211&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0xZTYwNmRmMjM1MmU2MzAzMDYzYjdhMTMzNGQxNjIxMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e57795932479f8b57108726e500fa9c1760c2e8f1243b6042cc362c03dfac659JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2325e62e1e33f561bfd232334e17c5a9ae5209b213fb80e8570389fd31e90f99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11a6530caae8c2f43b01f6b4a0abb1efc4dd3b04dd688e45a7b9aca90cedd1c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f959bdc42a8c9e48350c871ab36c0ab697db017fdd882815a942040dbbade35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3904acca6f83214d0ec9484a4d782f127b667d10eeb207510f35621b2a555f0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20vbG9naW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a43d7edf0e08044c3ad961d05a278f81e1da7ae8020552bb4c9e6b96323c949JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX05laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d73cf733e17bcb7ad784a1ecda0d06b75b622fce90e83e470b40c55e351992eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecee449cb907baccc2552b797be2614c94b7844806b8089492ac1db5704a3f7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc736d65015dd835b3de9d0151ac79dac621dcd0e06d401bb99a8a1fde2e97f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=836616998f4d8e76524355b672375a6164c4b83687e6a228864a152dc0e6295eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e3f9143-6a83-60af-2d91-86a26b246120&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1HQ2R3S2hUdE5Odw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=457dc8c7b17c24b32cd0be6762126c82021b43ccd027be98e49c6bfebdb9b36eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MWE3NmY1NWU2ZWMwNjdkMjEyNzhlMmJmNmY5NjY2NjI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8dc2e36d1eab22ee146b6f41eab89b19f60e53f57108d34841ff3bde48cfebaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19ec86ab9d7b3f1340083a0707854f8eaa2cac8bb92213df3f1d9f84216033baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b5da55df008ac49c290d4ea46169f1e2f0ab8137e59637ecdbca58f740f7a7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb8dca24adb9b0a79d98e2394f5ef59dce3ac9c7835da10633c76e545e15e31aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9sYWNvdW50eS5nb3YvcmVzaWRlbnRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39c37090d1afa7df144c019735e709db69dc41e90889073649defe4fc1c48576JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=403799c010bb81bb216f380e7c59c5705c1c89e9fcd667b3f4c5c4bde4901164JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f16d91aed198cca04fd113d2bffd0260fbc955b14494686a51a81b3851f73d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca4df5116d2ddb7b9acc7fceea53a694f60bdb5681fa8358e1294e93aa416395JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be6ea7ecd02123ea9edd6cf083a61fc8df57dccaf0850b952fe816906e1ec498JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a76f55e-6ec0-67d2-1278-e2bf6f966662&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7996d8292a81858a627fc7d5abfcba95639670bce09e6716caf9ff8c4453d40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd5a69d180192451fc074d2622cef56da649dc26ca3bf5ba1423515fefe28903JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=756ffb1f9cf31aa2fff28fa4d84ea5106bf0d9490a2104718fca3af428b7009dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3ByZW1pZXItbGVhZ3VlL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cd165f28a2391b60295a0254b5a00055728a510642a374018d0f04a80dc5fd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL2NoYW1waW9uc2hpcC9zY29yZXMtZml4dHVyZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f6dad3e8461218a7af3c237b0c0b207ce32ae2af17cd47a9526d278314d94ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3ByZW1pZXItbGVhZ3Vl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae56f9d6cbbf9126d3d41b29f1ee42dd603595c637fca1c08a0cefa3b06cb114JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L3J1Z2J5LXVuaW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e949d802f3ef8cf398c6845a64ec146c1b3911c49a75a9e77e22f7c34a566418JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2NyaWNrZXQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ef0f1b3ceb4482fddb9b79ee971df3f98796784edf314dd3bed2a1b20066822JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3Njb3R0aXNoLXByZW1pZXJzaGlwL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44f334d83a24df1e564a5b01e342d480ce48a1bfd0806708133fc14b671c1ab8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL2lyaXNoL3Njb3Jlcy1maXh0dXJlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99d5ce89e56a71def639ab660bcd46aaa4bff723f3cc17ff9d6393216c618461JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1dd0d406-b495-6a40-2dd1-c3e7b59a6bb4&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL3Nwb3J0L2Zvb3RiYWxsL3RlYW1zL2VuZ2xhbmQvc2NvcmVzLWZpeHR1cmVz&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b48579e951af1ee2505196b37872101ad2ab6cbaf839a09e126edb9d5700e198JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1421d3c9a55e92c48288dfb41a2caafe8c0895268672a682ea6bb535fe88e95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a614cab15687261955946a60b67825067b9de5c7b54b89182d4505c04b84fbc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f999766a32ee6641244536b981e51fc3313db9aca4cfca06d69ce2da5d34b4eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a93ab1db0cbff293cbf742abe9027c1c1524c177e5598e14f535fceff3ae9f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5a59f680bc6eea1a1a379b59ac8c9b285cfa065525c3ed3ca92789f695f4abaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0eeebf01b7374b144065f802bef390adc0feeb803b49819f7ac5b4929cc24376JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb28e72a881f9d4f81c77d22e45348b315f12f977aaf7f24ebd558e8e71eb742JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c60a1123ab13f13ba4ba9740522cacd4b1b6fbe298919e0a71e1472ac8b967c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9347cab528105286f375712a7c6591f80a410935b9b5693c5d36b4e4c857834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31bded775fee0e32b14d91e5b28231e075c9a6776af12c0191aba90e6002eba9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b098fd83f0c2be26859c51a17d4388c69c30832aef6c566e1087d70f8299a00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc0d103ae03de399873304606177fd2589975fc64f59e2cf7cfed6cb15219fb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d68c0b80e0145b49dbefa18dadd03244bfea11c25d8c42aba4451b79a5f9d85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aab56d8ebeed6650d6aa51620e95bf86df1dbce262389bcaacd5037926a2b976JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3232a8b9b7dc94c4747401b4129e525ccd88943367c6306328b7747b98686e21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=122178056620948d4789e2008113597138a5c881cac6c3a4f4bb1dfecd0f6055JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0yOTc5MTMyZWZmOGY2MTg5Mzk1MDA0Y2ZmZTk0NjAyMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ed40a1316b14aa5c23d78364548e4f3c1c62cbe5ce80cb2e264a89cd25d9b96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9jYXJzLnVzbmV3cy5jb20vY2Fycy10cnVja3MvaG9uZGEvY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c43ed506ad7a33ea028b13f68856793f2cc76788ebe0c7e8aa71351475d2bdeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2Fycy5jb20vcmVzZWFyY2gvaG9uZGEtY2l2aWMvP21zb2NraWQ9Mjk3OTEzMmVmZjhmNjE4OTM5NTAwNGNmZmU5NDYwMjA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8da724a07b962d4cfa82db7a37247a87b5ca61f5d7c2f87e46307d9b176f4bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYz9tc29ja2lkPTI5NzkxMzJlZmY4ZjYxODkzOTUwMDRjZmZlOTQ2MDIw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de6c9f82a0a190679b44513d593c83dc2b950d3165187cfbbedafec43d326b80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b7a3bf212863a331587b5a836d3f9421b26e412b199269d4a449d708d1dfc77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3efce697ad2e8d74bbbce45a41e2ad9b00bde0797081dcc9c5492bded3e05130JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee84d0e40be28bc8cc48e2eb5065915636d4a47847aad51d92acf277657ff7e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d01045913a7fe69def97e3dc2889461f59eb8abab5ac8f3598fe6fedcffdb37aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6c2b6f97404758215a436fec47a196c0475c4efc95d7e975f66d346cf2ab13aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9759b947d7260ffbe5471523c2730e968ec48ba64ddb73700149b207ff855b56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX05laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1c28ca89d5efea78092fdaf9b4b8aeed04473923bb8721ca8198feb5818d741JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20vbG9naW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e5b577d4ab4c97a65aee4b36f15624bd9ac58e666187c3ed1d38bf9e25b11b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1ee75dc7a67c05a8e7ec80d1dfd0444d52ee0c33a064f9e52330014b2d2c3c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44d28a9df1ffd667668ebfc04008c3e3c1e405d80fa9bf732f16a85b968178d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=363872cd41e4a67760096f0d372ee208b1bfe513716537b92286ddaa3be38ff6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL25ld3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4ccec8ea726c3fb11c50f950b318c2a268b1920ea4b6d6a311478cf2141e2deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cubm9ydGhlYXN0c2hvb3RlcnMuY29tL3hlbi90aHJlYWRzL3doYXQtd2FsbWFydC1zdGlsbC1zZWxscy1ndW5zLjUyNTI4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c454f254aa5d7f375d4fba5f847efe17b34b3d4c30f4daaba54387b136243e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cubm9ydGhlYXN0c2hvb3RlcnMuY29tL3hlbi90aHJlYWRzL3dhbG1hcnQtcnVnZXItMTAtMjItdnMtZ3Vuc2hvcC1ydWdlci0xMC0yMi41MjcwNy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc1c5b0c7ba83a6ac491ccca8c240bb2210287b973bbf352dd069fa5be316459JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0dhbWluZ0xlYWtzQW5kUnVtb3Vycy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2ee21111976570ab5ae62ca125f18de77d2f2a282b49a207f2f45261792339eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0FJVEFILw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5796d11fc57855d77057897ca16dda0416b5e76aad9fbd94b3e9974d0df7b07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3dhbGxzdHJlZXRiZXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61e7f55db4e431578c3bff717dac36602917421c0bffd583ab12eabee19dbca6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0xlZ29sZWFrLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7515857a46b9a4d5775ef6ed686046e6dec09a7e650c7e9fef4058854a635f92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2Z1bm55Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50279e4be9722378f1d8b0593725a08747ddde8090a873029eae00582d16ebc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlZGRpdC93aWtpL2luZGV4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8a4efa4a2d49b446faca6c6a3ce515788e38e0bf9784731a711d569a2094889JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52e1fd39225b254594427eb6278e6422c1654c743a87d51039594f056bf1ece8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MjkzYWZmMmNlN2QyNjVkZDM1ZTVlOGNkZTY5ZTY0MTc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9bfee758819e0fbbd8d2e1d77bd9aef61a8afe42b8a391715c44ea1766993cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f58c519877a45cf4dce9b7df6b9a53115be25940771e2605b1ec0ad0621e05aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cubWljaGlnYW5yZXNpZGVudGRhdGFiYXNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b9fb552ef095b016cf4642cf21465ae367834032d73ed35319266636f83723aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cbf741bc60f7a50c8f9dde8499eaf6fa157f790d7084a4a2cac094476586be4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=006d04724ef53cb51e44cbbfc1a19cded8404eaa662b2ee205623b7dc366ee3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07ab5d5ac32cb1543c3a5619392e1a664281992a3532dd132fbf9d8fd29aa756JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d928bba71f90975b18648fb57a535dd5bb87f36e087963f8d9ed88db39f34e15JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1deb87ae026e193f78c5e3eaa8038554c4066516e88d63cf3efecb1437934aa8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ3IyeGRUWXJZLVEwMlBWZWJyVGRnaVE&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
-  </si>
-  <si>
-    <t>Green Point</t>
   </si>
   <si>
     <t>Bing</t>
@@ -743,7 +740,7 @@
         <v>110</v>
       </c>
       <c r="H2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -763,7 +760,7 @@
         <v>110</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -783,7 +780,7 @@
         <v>110</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -803,7 +800,7 @@
         <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -823,7 +820,7 @@
         <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -843,7 +840,7 @@
         <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -863,7 +860,7 @@
         <v>110</v>
       </c>
       <c r="H8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -883,7 +880,7 @@
         <v>110</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -903,7 +900,7 @@
         <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -923,7 +920,7 @@
         <v>110</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -943,7 +940,7 @@
         <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -963,7 +960,7 @@
         <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -983,7 +980,7 @@
         <v>110</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1003,7 +1000,7 @@
         <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1023,7 +1020,7 @@
         <v>110</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1043,7 +1040,7 @@
         <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1063,7 +1060,7 @@
         <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1083,7 +1080,7 @@
         <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1103,7 +1100,7 @@
         <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1123,7 +1120,7 @@
         <v>110</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1143,7 +1140,7 @@
         <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1163,7 +1160,7 @@
         <v>110</v>
       </c>
       <c r="H23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1183,7 +1180,7 @@
         <v>110</v>
       </c>
       <c r="H24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1203,7 +1200,7 @@
         <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1223,7 +1220,7 @@
         <v>110</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1243,7 +1240,7 @@
         <v>110</v>
       </c>
       <c r="H27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1263,7 +1260,7 @@
         <v>110</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1283,7 +1280,7 @@
         <v>110</v>
       </c>
       <c r="H29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1303,7 +1300,7 @@
         <v>110</v>
       </c>
       <c r="H30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1323,7 +1320,7 @@
         <v>110</v>
       </c>
       <c r="H31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1343,7 +1340,7 @@
         <v>110</v>
       </c>
       <c r="H32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1363,7 +1360,7 @@
         <v>110</v>
       </c>
       <c r="H33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1383,7 +1380,7 @@
         <v>110</v>
       </c>
       <c r="H34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1403,7 +1400,7 @@
         <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1423,7 +1420,7 @@
         <v>110</v>
       </c>
       <c r="H36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1443,7 +1440,7 @@
         <v>110</v>
       </c>
       <c r="H37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1463,7 +1460,7 @@
         <v>110</v>
       </c>
       <c r="H38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1483,7 +1480,7 @@
         <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1503,7 +1500,7 @@
         <v>110</v>
       </c>
       <c r="H40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1523,7 +1520,7 @@
         <v>110</v>
       </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1540,10 +1537,10 @@
         <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1560,10 +1557,10 @@
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1580,10 +1577,10 @@
         <v>102</v>
       </c>
       <c r="G44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1600,10 +1597,10 @@
         <v>103</v>
       </c>
       <c r="G45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1620,10 +1617,10 @@
         <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1640,10 +1637,10 @@
         <v>105</v>
       </c>
       <c r="G47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1660,10 +1657,10 @@
         <v>106</v>
       </c>
       <c r="G48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1680,10 +1677,10 @@
         <v>107</v>
       </c>
       <c r="G49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1700,10 +1697,10 @@
         <v>108</v>
       </c>
       <c r="G50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1720,10 +1717,10 @@
         <v>109</v>
       </c>
       <c r="G51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="90">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,36 +40,36 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Community Information-West Bloomfield Township,Michigan</t>
-  </si>
-  <si>
-    <t>Official Website ofWest Bloomfield Township,MI</t>
-  </si>
-  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home - Bloomfield Township</t>
-  </si>
-  <si>
-    <t>West Bloomfield Twp,MI- Facebook</t>
-  </si>
-  <si>
-    <t>Home - WB Parks</t>
-  </si>
-  <si>
-    <t>West Bloomfield Township,Michigan-Wikipedia</t>
-  </si>
-  <si>
-    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
+    <t>SeattleDepartment ofNeighborhoods</t>
+  </si>
+  <si>
+    <t>Community(TV Series 2009–2015) - IMDb</t>
+  </si>
+  <si>
+    <t>CommunityCenters - Parks |seattle.gov</t>
   </si>
   <si>
     <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
   </si>
   <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>What is aCommunity? (14 Key Points) - Simplicable</t>
+  </si>
+  <si>
+    <t>Key Characteristics That Define aCommunity- Sociology Institute</t>
+  </si>
+  <si>
+    <t>COMMUNITY| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
   </si>
   <si>
@@ -82,22 +82,22 @@
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
+    <t>New &amp; Used HondaCivicNearBrea,CA- Hardin Honda</t>
+  </si>
+  <si>
+    <t>Facilities•Civic&amp; Cultural Center -Brea,CA</t>
+  </si>
+  <si>
+    <t>Used Honda Civicfor Sale nearBrea,CA- CarGurus</t>
+  </si>
+  <si>
+    <t>Honda Dealer ServingBrea,CA- Sales, Service, Specials, Parts ...</t>
+  </si>
+  <si>
     <t>Honda Civic For Sale- Carsforsale.com®</t>
   </si>
   <si>
-    <t>HondaCivic(eleventh generation) - Wikipedia</t>
-  </si>
-  <si>
-    <t>2026Honda CivicPrice, Reviews, Pictures &amp; More | Kelley Blue Book</t>
-  </si>
-  <si>
-    <t>2026Honda CivicReview, Pricing, &amp; Pictures | U.S. News</t>
-  </si>
-  <si>
-    <t>Honda Civic: Prices, Specs &amp; Features by Year | Cars.com</t>
-  </si>
-  <si>
-    <t>Used HondaCivicfor Sale Near Me - Autotrader</t>
+    <t>Used HondaCivicfor Sale Near Me inBrea,CA- Autotrader</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -109,85 +109,52 @@
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
-    <t>TheNeighbourhood- Wourld Tour</t>
-  </si>
-  <si>
-    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>Nextdoor - Discover yourneighbourhood</t>
-  </si>
-  <si>
     <t>The Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>Login - Nextdoor</t>
-  </si>
-  <si>
-    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
+    <t>TheNeighbourhood- 2026 Tour Dates &amp; Concert Schedule - Live Nation</t>
   </si>
   <si>
     <t>The Neighbourhood-YouTube</t>
   </si>
   <si>
-    <t>Reddit - Dive into anything</t>
-  </si>
-  <si>
-    <t>News - Reddit</t>
-  </si>
-  <si>
-    <t>What WalMart still sells guns???? - Northeastshooters.com Forums</t>
-  </si>
-  <si>
-    <t>Walmart Ruger 10/22 vs. Gunshop Ruger 10/22</t>
-  </si>
-  <si>
-    <t>r/GamingLeaksAndRumours | Central hub for ALL gaming leaks</t>
-  </si>
-  <si>
-    <t>AITAH - Reddit</t>
-  </si>
-  <si>
-    <t>r/wallstreetbets - Reddit</t>
-  </si>
-  <si>
-    <t>LegoLeak - Reddit</t>
-  </si>
-  <si>
-    <t>r/funny - Reddit</t>
-  </si>
-  <si>
-    <t>reddit</t>
+    <t>The NeighbourhoodTickets, Tour Dates &amp; Concerts 2027 &amp; 2026 -Songkick</t>
+  </si>
+  <si>
+    <t>The Neighbourhood Tickets&amp; 2026 Tour Dates |Vivid Seats</t>
+  </si>
+  <si>
+    <t>The Neighbourhood Tickets, 2026-2027 Concert Tour Dates</t>
+  </si>
+  <si>
+    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
+  </si>
+  <si>
+    <t>The Residents-Wikipedia</t>
   </si>
   <si>
     <t>The Residents Official Site</t>
   </si>
   <si>
-    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
-  </si>
-  <si>
-    <t>The Residents-Wikipedia</t>
-  </si>
-  <si>
-    <t>MichiganResidentsDatabase Search</t>
-  </si>
-  <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
     <t>Live &amp; Preserved - TheResidents</t>
   </si>
   <si>
-    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
     <t>RESIDENT| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
-    <t>The Residents - Topic-YouTube</t>
+    <t>The Resident (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Free Reverse Address Lookup - TruePeopleSearch</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -196,154 +163,121 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b48579e951af1ee2505196b37872101ad2ab6cbaf839a09e126edb9d5700e198JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1421d3c9a55e92c48288dfb41a2caafe8c0895268672a682ea6bb535fe88e95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a614cab15687261955946a60b67825067b9de5c7b54b89182d4505c04b84fbc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f999766a32ee6641244536b981e51fc3313db9aca4cfca06d69ce2da5d34b4eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a93ab1db0cbff293cbf742abe9027c1c1524c177e5598e14f535fceff3ae9f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5a59f680bc6eea1a1a379b59ac8c9b285cfa065525c3ed3ca92789f695f4abaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0eeebf01b7374b144065f802bef390adc0feeb803b49819f7ac5b4929cc24376JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb28e72a881f9d4f81c77d22e45348b315f12f977aaf7f24ebd558e8e71eb742JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c60a1123ab13f13ba4ba9740522cacd4b1b6fbe298919e0a71e1472ac8b967c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9347cab528105286f375712a7c6591f80a410935b9b5693c5d36b4e4c857834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ab79c0c-4632-623d-0a43-8bed47836302&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31bded775fee0e32b14d91e5b28231e075c9a6776af12c0191aba90e6002eba9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b098fd83f0c2be26859c51a17d4388c69c30832aef6c566e1087d70f8299a00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc0d103ae03de399873304606177fd2589975fc64f59e2cf7cfed6cb15219fb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d68c0b80e0145b49dbefa18dadd03244bfea11c25d8c42aba4451b79a5f9d85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aab56d8ebeed6650d6aa51620e95bf86df1dbce262389bcaacd5037926a2b976JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3232a8b9b7dc94c4747401b4129e525ccd88943367c6306328b7747b98686e21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=122178056620948d4789e2008113597138a5c881cac6c3a4f4bb1dfecd0f6055JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0yOTc5MTMyZWZmOGY2MTg5Mzk1MDA0Y2ZmZTk0NjAyMA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ed40a1316b14aa5c23d78364548e4f3c1c62cbe5ce80cb2e264a89cd25d9b96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly9jYXJzLnVzbmV3cy5jb20vY2Fycy10cnVja3MvaG9uZGEvY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c43ed506ad7a33ea028b13f68856793f2cc76788ebe0c7e8aa71351475d2bdeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuY2Fycy5jb20vcmVzZWFyY2gvaG9uZGEtY2l2aWMvP21zb2NraWQ9Mjk3OTEzMmVmZjhmNjE4OTM5NTAwNGNmZmU5NDYwMjA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8da724a07b962d4cfa82db7a37247a87b5ca61f5d7c2f87e46307d9b176f4bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2979132e-ff8f-6189-3950-04cffe946020&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYz9tc29ja2lkPTI5NzkxMzJlZmY4ZjYxODkzOTUwMDRjZmZlOTQ2MDIw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de6c9f82a0a190679b44513d593c83dc2b950d3165187cfbbedafec43d326b80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b7a3bf212863a331587b5a836d3f9421b26e412b199269d4a449d708d1dfc77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3efce697ad2e8d74bbbce45a41e2ad9b00bde0797081dcc9c5492bded3e05130JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee84d0e40be28bc8cc48e2eb5065915636d4a47847aad51d92acf277657ff7e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d01045913a7fe69def97e3dc2889461f59eb8abab5ac8f3598fe6fedcffdb37aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6c2b6f97404758215a436fec47a196c0475c4efc95d7e975f66d346cf2ab13aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9759b947d7260ffbe5471523c2730e968ec48ba64ddb73700149b207ff855b56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX05laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1c28ca89d5efea78092fdaf9b4b8aeed04473923bb8721ca8198feb5818d741JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20vbG9naW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e5b577d4ab4c97a65aee4b36f15624bd9ac58e666187c3ed1d38bf9e25b11b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1ee75dc7a67c05a8e7ec80d1dfd0444d52ee0c33a064f9e52330014b2d2c3c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3423d041-c03c-60bd-269e-c7a0c11261c5&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44d28a9df1ffd667668ebfc04008c3e3c1e405d80fa9bf732f16a85b968178d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=363872cd41e4a67760096f0d372ee208b1bfe513716537b92286ddaa3be38ff6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL25ld3Mv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4ccec8ea726c3fb11c50f950b318c2a268b1920ea4b6d6a311478cf2141e2deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cubm9ydGhlYXN0c2hvb3RlcnMuY29tL3hlbi90aHJlYWRzL3doYXQtd2FsbWFydC1zdGlsbC1zZWxscy1ndW5zLjUyNTI4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c454f254aa5d7f375d4fba5f847efe17b34b3d4c30f4daaba54387b136243e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cubm9ydGhlYXN0c2hvb3RlcnMuY29tL3hlbi90aHJlYWRzL3dhbG1hcnQtcnVnZXItMTAtMjItdnMtZ3Vuc2hvcC1ydWdlci0xMC0yMi41MjcwNy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc1c5b0c7ba83a6ac491ccca8c240bb2210287b973bbf352dd069fa5be316459JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0dhbWluZ0xlYWtzQW5kUnVtb3Vycy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2ee21111976570ab5ae62ca125f18de77d2f2a282b49a207f2f45261792339eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0FJVEFILw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5796d11fc57855d77057897ca16dda0416b5e76aad9fbd94b3e9974d0df7b07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3dhbGxzdHJlZXRiZXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61e7f55db4e431578c3bff717dac36602917421c0bffd583ab12eabee19dbca6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0xlZ29sZWFrLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7515857a46b9a4d5775ef6ed686046e6dec09a7e650c7e9fef4058854a635f92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2Z1bm55Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50279e4be9722378f1d8b0593725a08747ddde8090a873029eae00582d16ebc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1014e92c-ca1a-6c3e-16e9-fecdcb3d6dd5&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlZGRpdC93aWtpL2luZGV4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8a4efa4a2d49b446faca6c6a3ce515788e38e0bf9784731a711d569a2094889JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52e1fd39225b254594427eb6278e6422c1654c743a87d51039594f056bf1ece8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MjkzYWZmMmNlN2QyNjVkZDM1ZTVlOGNkZTY5ZTY0MTc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9bfee758819e0fbbd8d2e1d77bd9aef61a8afe42b8a391715c44ea1766993cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f58c519877a45cf4dce9b7df6b9a53115be25940771e2605b1ec0ad0621e05aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cubWljaGlnYW5yZXNpZGVudGRhdGFiYXNlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b9fb552ef095b016cf4642cf21465ae367834032d73ed35319266636f83723aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cbf741bc60f7a50c8f9dde8499eaf6fa157f790d7084a4a2cac094476586be4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=006d04724ef53cb51e44cbbfc1a19cded8404eaa662b2ee205623b7dc366ee3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07ab5d5ac32cb1543c3a5619392e1a664281992a3532dd132fbf9d8fd29aa756JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d928bba71f90975b18648fb57a535dd5bb87f36e087963f8d9ed88db39f34e15JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1deb87ae026e193f78c5e3eaa8038554c4066516e88d63cf3efecb1437934aa8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293aff2c-e7d2-65dd-35e5-e8cde69e6417&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ3IyeGRUWXJZLVEwMlBWZWJyVGRnaVE&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=269cab2c8d1f5b2158c110018f4b052284b71ecb7c1305acf53040d96f31db21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51b04a09ba49811fbf6dc543afaaf91979e0b354b151e7377b666b88b57cf6a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fef76c1416478720cfb99bcff4bc0340f022b78a98819c128e4c3a03ab833a25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvbmVpZ2hib3Job29kcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=158c1b2341f3f444e838db6376116fb183b66e1182bcfb3e444e9434180e3df7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNDM5NjI5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d1846eeddfd183a1bbfdf1f91353fc21d643cc860f1e143eb66f376b7bc2799JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvcGFya3MvY29tbXVuaXR5LWNlbnRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74b2fa6eba6a6049c979bfa10a2a290f81351c2e38b2b812b35cda143ee24964JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb3cec9d38b84854eb67564da0de88a1d7a3c8b0f21a72faf49a5860088c2d6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed587a571f4ac9da6428a4e3864b1f63f36f41c82bbb082e8967e5de894cf265JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWNvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcb21f5abb953ff5b3541d32c15ae9885c12b7018aaa288cb16a787b7167ecc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvY2hhcmFjdGVyaXN0aWNzLWRlZmluaW5nLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eab17bd940e3e24f1890bceff114ee0d23f7e83c4764dc12e114ff192dcf2a20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ee1cfadd6b5b7ad3b85501cde0e49682b6d424d4e340eb5d3b9eb38f609976JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebc4bab345d9e26f0549e4ba943a5f000da0faa8985a3f7a138e4c4de99cf15fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f61f9c1928dfaa84dbbb347f1de3e5365a9bace74a90a6a36391e5ef33f4256JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=371b3cd116364dbe6d6e8a4f6a0573557077dd1c1e0520f2d3479db92d24ffefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a89848545e94803a1fad4455e5a4281ee637cdfd397db8c8af04f44bf07f7046JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=166f314998ea1cc9e26f4553b4ca66fa35b8a69279d5be2ed9b91dfcd2506182JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1dec6b12fa2dd5676037c30c2a35134e33d624ac44abb37bd0608c8134a3674JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTM5NDM1ZDgzNWQ2MzY1OTMyMTNiNGE2MjVjZWI2NGI1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7167fce0e85a7186d4f7b8ffc58acc32eca3671575bc1bf1a22ea75218cdb5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c79c0e215e2548dae3b59d0fc9e759f8e9cd685b3a089bc7f054b628d55ba9c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72e934053376b23affe81c3b86e0bd6856991f771c302aa7658d292d66040d11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9Mzk0MzVkODM1ZDYzNjU5MzIxM2I0YTYyNWNlYjY0YjU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59fd1367006c82c96f6167bd935a0c4f8ff0b6980dc4bec8ac8781c33e07bd30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e7ae3c7f69f364c7b16d7f76fd23c5916e233fe9bb83fb2f8d8fb1a4742b1b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d0c9d05d8fb90950afe5234f2b2a444f4063010c577fa647d3ab668fb4a623bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef1a28e871c08bab914740c04456508b8a0c703adfc328bcb9e2e4025f396508JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1882d7f68d73f48aaf2aa2cf1387020c5f69a071f3f715f47320f7155333a55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85b68e6e3bf5eac4bfb6bfb38e3e620825be5a0f804f3ed4ce8c65cc80d14374JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6810885fd3dadfd344fcca47d4afb8d69668304b633111dd74b95a567b315ac2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1442a7c2283b0c9ea801fe8627a33c80ffdb299c85aadda428f7544383d0e287JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0zNmZmYzViZGZmZDA2YzE1M2NmMWQyNWNmZTBmNmRlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2adb2215e71483903cbb5360caf502e7e2bb36c7a84a2b8f3d2906b4e9ea53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MzZmZmM1YmRmZmQwNmMxNTNjZjFkMjVjZmUwZjZkZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30bcb66ae3f17ce4ebd4056b6c5d63c8982ad3991dc558d515561e8f655df2fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MTRlYzBjNzE3Mjk0NmQ2MzIxOWQxYjkwNzNmMjZjM2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53e7c6b039157667328a2ad0bfc7077843e7d33cafbc2895ef730427f98f919dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04d1742a0764029f0774af0951389111fd3b5f60d7f0f07acbc7441ab916fbc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79b673f9033cfd10cf56ecafbf0e24da9805a59c4338aa3034c54bed73e0310aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1b12dda3a55ba792bcfc2eb4405f7c34cf99b030cc5786a711e2384bbf88a68JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d193d0ffd236020767f3972ffd09e37134998565490c73f006b63a7b52547cfcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df956de030a08fab66833ebee01e5eea19af99a74f27d87577385d5abe047a85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c0ddb2755e296cfbba6fe4607c5c0fb4be6683f2a48681005b2712fc6ae781dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d6344092738f903086b3a500bc63196985a17f0c09137ea61a81dfa687ceca7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3624d5b990655811c700c6a3a2fe3883966fbb6aaa910cc1ac33090dbe631a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -694,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -728,19 +662,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -748,19 +682,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -768,19 +702,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -788,19 +722,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -808,19 +742,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -828,19 +762,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -848,19 +782,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -868,19 +802,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -888,19 +822,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -908,19 +842,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -928,19 +862,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -948,19 +882,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -968,19 +902,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -988,19 +922,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1008,19 +942,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1028,19 +962,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1048,19 +982,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1068,19 +1002,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1088,19 +1022,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1108,19 +1042,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1128,19 +1062,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1148,19 +1082,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1168,19 +1102,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1188,19 +1122,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1208,19 +1142,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1228,19 +1162,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1248,19 +1182,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1268,19 +1202,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1288,19 +1222,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1308,19 +1242,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1328,19 +1262,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1348,19 +1282,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1368,19 +1302,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1388,19 +1322,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1408,19 +1342,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1428,19 +1362,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1448,19 +1382,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G38" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1468,19 +1402,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1488,239 +1422,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" t="s">
-        <v>110</v>
-      </c>
-      <c r="H41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>110</v>
-      </c>
-      <c r="H42" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>110</v>
-      </c>
-      <c r="H43" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G44" t="s">
-        <v>110</v>
-      </c>
-      <c r="H44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G45" t="s">
-        <v>110</v>
-      </c>
-      <c r="H45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46" t="s">
-        <v>110</v>
-      </c>
-      <c r="H46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G47" t="s">
-        <v>110</v>
-      </c>
-      <c r="H47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G48" t="s">
-        <v>110</v>
-      </c>
-      <c r="H48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G49" t="s">
-        <v>110</v>
-      </c>
-      <c r="H49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G50" t="s">
-        <v>110</v>
-      </c>
-      <c r="H50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1764,17 +1478,6 @@
     <hyperlink ref="F38" r:id="rId37"/>
     <hyperlink ref="F39" r:id="rId38"/>
     <hyperlink ref="F40" r:id="rId39"/>
-    <hyperlink ref="F41" r:id="rId40"/>
-    <hyperlink ref="F42" r:id="rId41"/>
-    <hyperlink ref="F43" r:id="rId42"/>
-    <hyperlink ref="F44" r:id="rId43"/>
-    <hyperlink ref="F45" r:id="rId44"/>
-    <hyperlink ref="F46" r:id="rId45"/>
-    <hyperlink ref="F47" r:id="rId46"/>
-    <hyperlink ref="F48" r:id="rId47"/>
-    <hyperlink ref="F49" r:id="rId48"/>
-    <hyperlink ref="F50" r:id="rId49"/>
-    <hyperlink ref="F51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -43,31 +43,31 @@
     <t>Community-Wikipedia</t>
   </si>
   <si>
+    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+  </si>
+  <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | 211LA</t>
+  </si>
+  <si>
+    <t>California Community Foundation| A Good Life for All</t>
+  </si>
+  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>SeattleDepartment ofNeighborhoods</t>
-  </si>
-  <si>
     <t>Community(TV Series 2009–2015) - IMDb</t>
   </si>
   <si>
-    <t>CommunityCenters - Parks |seattle.gov</t>
-  </si>
-  <si>
-    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>What is aCommunity? (14 Key Points) - Simplicable</t>
-  </si>
-  <si>
-    <t>Key Characteristics That Define aCommunity- Sociology Institute</t>
-  </si>
-  <si>
-    <t>COMMUNITY| definition in the Cambridge English Dictionary</t>
+    <t>Community– Parks &amp; Recreation</t>
+  </si>
+  <si>
+    <t>Homepage |LACCD</t>
+  </si>
+  <si>
+    <t>Home | Neighborhood Info</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
@@ -163,121 +163,121 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=269cab2c8d1f5b2158c110018f4b052284b71ecb7c1305acf53040d96f31db21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51b04a09ba49811fbf6dc543afaaf91979e0b354b151e7377b666b88b57cf6a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fef76c1416478720cfb99bcff4bc0340f022b78a98819c128e4c3a03ab833a25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvbmVpZ2hib3Job29kcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=158c1b2341f3f444e838db6376116fb183b66e1182bcfb3e444e9434180e3df7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNDM5NjI5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d1846eeddfd183a1bbfdf1f91353fc21d643cc860f1e143eb66f376b7bc2799JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvcGFya3MvY29tbXVuaXR5LWNlbnRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74b2fa6eba6a6049c979bfa10a2a290f81351c2e38b2b812b35cda143ee24964JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb3cec9d38b84854eb67564da0de88a1d7a3c8b0f21a72faf49a5860088c2d6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed587a571f4ac9da6428a4e3864b1f63f36f41c82bbb082e8967e5de894cf265JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWNvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcb21f5abb953ff5b3541d32c15ae9885c12b7018aaa288cb16a787b7167ecc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvY2hhcmFjdGVyaXN0aWNzLWRlZmluaW5nLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eab17bd940e3e24f1890bceff114ee0d23f7e83c4764dc12e114ff192dcf2a20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f078a18-291d-6936-167d-9df9286568d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ee1cfadd6b5b7ad3b85501cde0e49682b6d424d4e340eb5d3b9eb38f609976JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebc4bab345d9e26f0549e4ba943a5f000da0faa8985a3f7a138e4c4de99cf15fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f61f9c1928dfaa84dbbb347f1de3e5365a9bace74a90a6a36391e5ef33f4256JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=371b3cd116364dbe6d6e8a4f6a0573557077dd1c1e0520f2d3479db92d24ffefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a89848545e94803a1fad4455e5a4281ee637cdfd397db8c8af04f44bf07f7046JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=166f314998ea1cc9e26f4553b4ca66fa35b8a69279d5be2ed9b91dfcd2506182JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1dec6b12fa2dd5676037c30c2a35134e33d624ac44abb37bd0608c8134a3674JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTM5NDM1ZDgzNWQ2MzY1OTMyMTNiNGE2MjVjZWI2NGI1&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7167fce0e85a7186d4f7b8ffc58acc32eca3671575bc1bf1a22ea75218cdb5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c79c0e215e2548dae3b59d0fc9e759f8e9cd685b3a089bc7f054b628d55ba9c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72e934053376b23affe81c3b86e0bd6856991f771c302aa7658d292d66040d11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39435d83-5d63-6593-213b-4a625ceb64b5&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9Mzk0MzVkODM1ZDYzNjU5MzIxM2I0YTYyNWNlYjY0YjU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59fd1367006c82c96f6167bd935a0c4f8ff0b6980dc4bec8ac8781c33e07bd30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e7ae3c7f69f364c7b16d7f76fd23c5916e233fe9bb83fb2f8d8fb1a4742b1b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d0c9d05d8fb90950afe5234f2b2a444f4063010c577fa647d3ab668fb4a623bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef1a28e871c08bab914740c04456508b8a0c703adfc328bcb9e2e4025f396508JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1882d7f68d73f48aaf2aa2cf1387020c5f69a071f3f715f47320f7155333a55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85b68e6e3bf5eac4bfb6bfb38e3e620825be5a0f804f3ed4ce8c65cc80d14374JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6810885fd3dadfd344fcca47d4afb8d69668304b633111dd74b95a567b315ac2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1442a7c2283b0c9ea801fe8627a33c80ffdb299c85aadda428f7544383d0e287JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0zNmZmYzViZGZmZDA2YzE1M2NmMWQyNWNmZTBmNmRlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2adb2215e71483903cbb5360caf502e7e2bb36c7a84a2b8f3d2906b4e9ea53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36ffc5bd-ffd0-6c15-3cf1-d25cfe0f6ded&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MzZmZmM1YmRmZmQwNmMxNTNjZjFkMjVjZmUwZjZkZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30bcb66ae3f17ce4ebd4056b6c5d63c8982ad3991dc558d515561e8f655df2fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MTRlYzBjNzE3Mjk0NmQ2MzIxOWQxYjkwNzNmMjZjM2E&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53e7c6b039157667328a2ad0bfc7077843e7d33cafbc2895ef730427f98f919dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04d1742a0764029f0774af0951389111fd3b5f60d7f0f07acbc7441ab916fbc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79b673f9033cfd10cf56ecafbf0e24da9805a59c4338aa3034c54bed73e0310aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1b12dda3a55ba792bcfc2eb4405f7c34cf99b030cc5786a711e2384bbf88a68JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d193d0ffd236020767f3972ffd09e37134998565490c73f006b63a7b52547cfcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df956de030a08fab66833ebee01e5eea19af99a74f27d87577385d5abe047a85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c0ddb2755e296cfbba6fe4607c5c0fb4be6683f2a48681005b2712fc6ae781dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d6344092738f903086b3a500bc63196985a17f0c09137ea61a81dfa687ceca7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3624d5b990655811c700c6a3a2fe3883966fbb6aaa910cc1ac33090dbe631a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ec0c71-7294-6d63-219d-1b9073f26c3a&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2ddd96f3f6620e3f9d52d9bce7963ae2e2f8560520cf1d596b927fd12e0cecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3f4fe911774e8e0b90607b5c1415b0e6869dc53d95046e9f8643c9317802995JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ebb17354cc647ca5aa4b6b3d15718b4e566bb61966a6cdcca6b4b2f9531bb95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fc17ca09cc0ac954d3e2a50e341eaea84f85aa8e960ea477c249a1a61d897fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b40df0d2e2a96d67c9331c622fe7ddfe779c13c4fefd8e155eb737f5b58195aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b32d8b4967644bc3677a500de890ba5441254499ba2355a2b28929a7e16c6e2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a510d9929ea7ecae1d25163479c5e3ddecfbe3b7ca02fa07ac5531c87f617c53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bafec31fac4fc4aee75c0d5d7d872c6942f47abe04da23b04d02b6f7728a5e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bd3f73a960646cd5eace0267bfa0bca2c8c5998e52490a3dc3e6ea92b7b063cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04e1d3d9d9d035bf42eda2f5ad366f243adae7fc5960f1eecd0e0abcc331d98fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9abcd0dee6a1e2d6a78c14603ee5b7d33b1818028cf8cd9647179df0185af00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42108f63f5b55a04a30e4f7e633714cc54741c320fe1f43f501af8e5722e8697JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6dea5d4073d27207e55bdeeac19331f49c1f55b1bc8dabfc20da494212437a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539d68014e0420f60d4a071149844c6c47e9742cadd9c1821689625c276f01a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fa0fb44b7cee96d4d23901aceb7acbcb7446c44bf5c993f6b2f8461b80eeb16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=baeabd4ac0055202243ee75a144fa1404113ccf5bd65a1fce2f13460b0ddaaabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e186a63480842166e0561d7a2f029cfd687b776efeea2a80be7d4888657825eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTBkODBlNDRhZWM1NzY1NzQzMmFiZjNhYmVkYzQ2NGJh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ad54a8ed3940a71431d49c771a0e3e7d30617a721872514f30e3f6a19603fe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed0279064323f9a404cded1e804f7956649c6498742a3707bf0df93331c173baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3893d26a5281dbe77721262fb45a59574a3b2eae093886a9a1e1f7130a9b49adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9MGQ4MGU0NGFlYzU3NjU3NDMyYWJmM2FiZWRjNDY0YmE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b703b7eed9b2b80bca842ef4a4b6aff1ce0523f9cec27be65ab3e637c0a6072cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=191a6245f09405bdf24e3880dc3215f9282c5c735a97ab04b63dc149d678f4a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14bfc0bf077274705a0892a74b59b464ea1defb1d9c3f5ca854da94af278a445JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b24529a21666a582a824eae5a40897fb14e533f5a87d034286aa42984eebc82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c29982f26498456f59228501a4a73c5ebb38618b36b67e31135b7e1f963987caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=264891072da4fb530e628cec97ba4ee18faa8f5f4ce7143e6f7863a898f56b22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01a85a2190eb0a8dbd4d5c8c10a614b898a4c8238833448d5003d1c036257eaeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=693e559df97ccb3c3d8fbb16be1c2648aba59253e532b78360c7f5de27c15b01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0wYzJhZTZiODQwZjk2ZDRkMjc0MmYxNTk0MTg4NmM4OA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb978340cbf228844db69677f313d5bc64767dbe2e3090b4505363d8c10c77e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MGMyYWU2Yjg0MGY5NmQ0ZDI3NDJmMTU5NDE4ODZjODg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=374e66b642242f5314b28880b6bca6d8a3792ac99dd4e113603a2cfab14603aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MGQ2NjQxMjEyMmY0NmFiYjA0N2M1NmMwMjNkZDZiZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b04b26f1c9e95fd05f01b7ece9439522b987572406642dffcd782af5182a6614JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0afebc7713c28f173f0fe25db337d35da2669d88b1c4f851048e7384e817e9e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f939625fe3b06101a6b2b7b1ebefbfb3ecd1b36e3d28bd0f58d94f43b702edaeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a6a6076ef51e0d76581a5097d31cbb4856b52d749bf7a952c3182deedf5df53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d92f719f228783a53968bccfb11318972448eae01b4e2f589e2bbc18cada7cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebfbef4c03833c71f7b88becf59cfa3eee7da57936edfdfded3e9e31ca35fb11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f28e80dcda839b5787c7f66fc4b75da28bf51c7c15d25759e393de36d53d17aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=803b01fc8daa7e38459b77448e275837baa1f2e966a93d227d1db4fb3a3fcdeaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2a0cbbaa8f373db300ecc13a9f44941a374658f2596074b8fead540f6067d02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Community Information-West Bloomfield Township,Michigan</t>
+  </si>
+  <si>
+    <t>Official Website ofWest Bloomfield Township,MI</t>
+  </si>
+  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Home | 211LA</t>
-  </si>
-  <si>
-    <t>California Community Foundation| A Good Life for All</t>
-  </si>
-  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Community(TV Series 2009–2015) - IMDb</t>
-  </si>
-  <si>
-    <t>Community– Parks &amp; Recreation</t>
-  </si>
-  <si>
-    <t>Homepage |LACCD</t>
-  </si>
-  <si>
-    <t>Home | Neighborhood Info</t>
+    <t>Home - Bloomfield Township</t>
+  </si>
+  <si>
+    <t>West Bloomfield Twp,MI- Facebook</t>
+  </si>
+  <si>
+    <t>Home - WB Parks</t>
+  </si>
+  <si>
+    <t>West Bloomfield Township,Michigan-Wikipedia</t>
+  </si>
+  <si>
+    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
+  </si>
+  <si>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
@@ -82,22 +82,22 @@
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
-    <t>New &amp; Used HondaCivicNearBrea,CA- Hardin Honda</t>
-  </si>
-  <si>
-    <t>Facilities•Civic&amp; Cultural Center -Brea,CA</t>
-  </si>
-  <si>
-    <t>Used Honda Civicfor Sale nearBrea,CA- CarGurus</t>
-  </si>
-  <si>
-    <t>Honda Dealer ServingBrea,CA- Sales, Service, Specials, Parts ...</t>
-  </si>
-  <si>
     <t>Honda Civic For Sale- Carsforsale.com®</t>
   </si>
   <si>
-    <t>Used HondaCivicfor Sale Near Me inBrea,CA- Autotrader</t>
+    <t>HondaCivic(eleventh generation) - Wikipedia</t>
+  </si>
+  <si>
+    <t>2026Honda CivicPrice, Reviews, Pictures &amp; More | Kelley Blue Book</t>
+  </si>
+  <si>
+    <t>2026Honda CivicReview, Pricing, &amp; Pictures | U.S. News</t>
+  </si>
+  <si>
+    <t>Honda Civic: Prices, Specs &amp; Features by Year | Cars.com</t>
+  </si>
+  <si>
+    <t>Used HondaCivicfor Sale Near Me - Autotrader</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -109,22 +109,28 @@
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
+    <t>TheNeighbourhood- Wourld Tour</t>
+  </si>
+  <si>
     <t>The Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>TheNeighbourhood- 2026 Tour Dates &amp; Concert Schedule - Live Nation</t>
-  </si>
-  <si>
     <t>The Neighbourhood-YouTube</t>
   </si>
   <si>
-    <t>The NeighbourhoodTickets, Tour Dates &amp; Concerts 2027 &amp; 2026 -Songkick</t>
-  </si>
-  <si>
-    <t>The Neighbourhood Tickets&amp; 2026 Tour Dates |Vivid Seats</t>
-  </si>
-  <si>
-    <t>The Neighbourhood Tickets, 2026-2027 Concert Tour Dates</t>
+    <t>Nextdoor - Discover yourneighbourhood</t>
+  </si>
+  <si>
+    <t>TheNeighbourhood- Sweater Weather (Official Video)</t>
+  </si>
+  <si>
+    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
+  </si>
+  <si>
+    <t>The Residents Official Site</t>
   </si>
   <si>
     <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
@@ -133,28 +139,25 @@
     <t>The Residents-Wikipedia</t>
   </si>
   <si>
-    <t>The Residents Official Site</t>
+    <t>MichiganResidentsDatabase Search</t>
   </si>
   <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Live &amp; Preserved - TheResidents</t>
+  </si>
+  <si>
     <t>RESIDENT| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
-    <t>Live &amp; Preserved - TheResidents</t>
-  </si>
-  <si>
     <t>RESIDENT| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
-    <t>The Resident (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Free Reverse Address Lookup - TruePeopleSearch</t>
+    <t>The Residents - Topic-YouTube</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -163,121 +166,124 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2ddd96f3f6620e3f9d52d9bce7963ae2e2f8560520cf1d596b927fd12e0cecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3f4fe911774e8e0b90607b5c1415b0e6869dc53d95046e9f8643c9317802995JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ebb17354cc647ca5aa4b6b3d15718b4e566bb61966a6cdcca6b4b2f9531bb95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fc17ca09cc0ac954d3e2a50e341eaea84f85aa8e960ea477c249a1a61d897fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b40df0d2e2a96d67c9331c622fe7ddfe779c13c4fefd8e155eb737f5b58195aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b32d8b4967644bc3677a500de890ba5441254499ba2355a2b28929a7e16c6e2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a510d9929ea7ecae1d25163479c5e3ddecfbe3b7ca02fa07ac5531c87f617c53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bafec31fac4fc4aee75c0d5d7d872c6942f47abe04da23b04d02b6f7728a5e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bd3f73a960646cd5eace0267bfa0bca2c8c5998e52490a3dc3e6ea92b7b063cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04e1d3d9d9d035bf42eda2f5ad366f243adae7fc5960f1eecd0e0abcc331d98fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f2e26ea-e2e1-692d-3db2-310be378682a&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9abcd0dee6a1e2d6a78c14603ee5b7d33b1818028cf8cd9647179df0185af00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42108f63f5b55a04a30e4f7e633714cc54741c320fe1f43f501af8e5722e8697JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6dea5d4073d27207e55bdeeac19331f49c1f55b1bc8dabfc20da494212437a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539d68014e0420f60d4a071149844c6c47e9742cadd9c1821689625c276f01a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fa0fb44b7cee96d4d23901aceb7acbcb7446c44bf5c993f6b2f8461b80eeb16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=baeabd4ac0055202243ee75a144fa1404113ccf5bd65a1fce2f13460b0ddaaabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e186a63480842166e0561d7a2f029cfd687b776efeea2a80be7d4888657825eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTBkODBlNDRhZWM1NzY1NzQzMmFiZjNhYmVkYzQ2NGJh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ad54a8ed3940a71431d49c771a0e3e7d30617a721872514f30e3f6a19603fe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed0279064323f9a404cded1e804f7956649c6498742a3707bf0df93331c173baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3893d26a5281dbe77721262fb45a59574a3b2eae093886a9a1e1f7130a9b49adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d80e44a-ec57-6574-32ab-f3abedc464ba&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9MGQ4MGU0NGFlYzU3NjU3NDMyYWJmM2FiZWRjNDY0YmE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b703b7eed9b2b80bca842ef4a4b6aff1ce0523f9cec27be65ab3e637c0a6072cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=191a6245f09405bdf24e3880dc3215f9282c5c735a97ab04b63dc149d678f4a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14bfc0bf077274705a0892a74b59b464ea1defb1d9c3f5ca854da94af278a445JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b24529a21666a582a824eae5a40897fb14e533f5a87d034286aa42984eebc82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c29982f26498456f59228501a4a73c5ebb38618b36b67e31135b7e1f963987caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=264891072da4fb530e628cec97ba4ee18faa8f5f4ce7143e6f7863a898f56b22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01a85a2190eb0a8dbd4d5c8c10a614b898a4c8238833448d5003d1c036257eaeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=693e559df97ccb3c3d8fbb16be1c2648aba59253e532b78360c7f5de27c15b01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0wYzJhZTZiODQwZjk2ZDRkMjc0MmYxNTk0MTg4NmM4OA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb978340cbf228844db69677f313d5bc64767dbe2e3090b4505363d8c10c77e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2ae6b8-40f9-6d4d-2742-f15941886c88&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MGMyYWU2Yjg0MGY5NmQ0ZDI3NDJmMTU5NDE4ODZjODg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=374e66b642242f5314b28880b6bca6d8a3792ac99dd4e113603a2cfab14603aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MGQ2NjQxMjEyMmY0NmFiYjA0N2M1NmMwMjNkZDZiZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b04b26f1c9e95fd05f01b7ece9439522b987572406642dffcd782af5182a6614JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0afebc7713c28f173f0fe25db337d35da2669d88b1c4f851048e7384e817e9e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f939625fe3b06101a6b2b7b1ebefbfb3ecd1b36e3d28bd0f58d94f43b702edaeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a6a6076ef51e0d76581a5097d31cbb4856b52d749bf7a952c3182deedf5df53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d92f719f228783a53968bccfb11318972448eae01b4e2f589e2bbc18cada7cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebfbef4c03833c71f7b88becf59cfa3eee7da57936edfdfded3e9e31ca35fb11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f28e80dcda839b5787c7f66fc4b75da28bf51c7c15d25759e393de36d53d17aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=803b01fc8daa7e38459b77448e275837baa1f2e966a93d227d1db4fb3a3fcdeaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2a0cbbaa8f373db300ecc13a9f44941a374658f2596074b8fead540f6067d02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d664121-22f4-6abb-047c-56c023dd6bed&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54de27898d7c1ba5940c6f87e5ad4cbdc6e17f6f15c0ee036334f28c1d67bf70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcd92ac1d627d1a63b14f3bda4bb71844a8a09d079448396f789717972ba881bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=650b00e0574f97ade896fa9dd9e508c75313dfc5629d4b9ee9213ed2e3473cc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c232f2dcf3280844b048e397fb3811b69ca9c0b962eb0f1c1fa3ba5003c4bf91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=847240b31e4920bfdde1da6f5c721a193a4b1fd6793ca0c9b648eedfa8a31a66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffc9520a5d714d96bea6edb519b81246ceecad6c74bd261851f1f1d458a1105cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c64254109421b7a648c17044335ff440a5e9767c28d4b96d5d430b4192075c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a097f728640d1def226fc66c5345ea1299c0b97faae35fe2076f311c39b07fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ca214dcbd3aa77185f1c46f147437001b2ff1b87eea7dfefc2a65707fbba8c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48e631c30594c17a3e09d330ddf4227295ee251865538ddb082cf29f6abc467fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064fcd156d7752a04be961544e964cd63b5062afbc14ade988a4333ca9b1f93cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6274d1c2b98278f0b26e0a0cc6ef21a467544ae78da13c2b3778d578376b3befJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5871783d9f8399a215c1a1201e06b64988e7d897c4b1b34f22f1a918037c4e0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d12df48da38a088b961cd0096bc5ef8d94c78b04308d99f97d23bff69425deeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a074658a0682f184c80899c5de24834ab8e85ab3a6d2a1d5c6319931ac0fb17aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=671810ee72e14fa5a314ed25f37863b331865c4e10731a10d55e09eba534fc86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=594aa24e660fd6c9c7f0689a5cb4ba074bbd069217eeea1a56a699cd13a9fbfcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0yOTNkYmNjMDA1Yzg2ZDczMDdlOGFiMjEwNGI1NmM3YQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5fdbef7acac471ac2cbedc4e3f9d91c51eb82613014e377b9f96518d43a10baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9jYXJzLnVzbmV3cy5jb20vY2Fycy10cnVja3MvaG9uZGEvY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f8ca1646bf6dfbe4da1f53cbda24310f28ad26bf06678a227f5bc2db36492e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2Fycy5jb20vcmVzZWFyY2gvaG9uZGEtY2l2aWMvP21zb2NraWQ9MjkzZGJjYzAwNWM4NmQ3MzA3ZThhYjIxMDRiNTZjN2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a2f1ecff59fd0e4fdff53a6975392105b4624887f881e391bfcd00e96fa87a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYz9tc29ja2lkPTI5M2RiY2MwMDVjODZkNzMwN2U4YWIyMTA0YjU2Yzdh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c86df2d4dc05fd8aa4cbb8f99e01dd04fef8110086e45b8b3cb38d258fb70c3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acc385d5646e30e6752794a3a0c416626596c2a4dff2b5c30d6770b179f282fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=578979cf0df6927a7c4b5b7675c91c7b2846648809673569000202e1542cd566JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4b67920829c31e4301677906818e0c24920effff023b1e1b2d8e7db3b353b84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71959afe0cd5b3198a37de9feed66eb949e0399c132d9272b8747eb27929909fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=134c5ed019cd7b7d8fdb62ff06eaf9eb2cbc74db6d2f170b256db07559d61ebbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9063a946e703fb09a93abca33897b1413a15c9b45bf82d9c94d4677299914c23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de3dd808b99a2319629bab57bd8d8ccee22ee766f44049f20d9b865de376c4ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9R0Nkd0toVHROTnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f775b402cc6925c9bab21840a1cb2d17d9fcb5ce2a58bcd2355f33467bf1983JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3e794ed2049b3bea980a2a5c14d6608b92a56110a499860c541637bec5f14bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c520720b7d7d588357ce3457b32c6dadd150feb16a9c53c5aa58f7543e60c9f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbef615717c29aafa98ea5755980de770852cd3a8f0c811095a09d9ff08ae762JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MjRjZjExODVlZjE0Njc3ODNlZTIwNjY0ZWUwMzY2YmI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22c5042eba755dcb9df244dd8ed2aad45e6741e29f311a06924a4228ac907e79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=054abb13ba9b66fd53e4fb3b1f9f76021816937f99cf0d7bc01d073e678dfc01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cubWljaGlnYW5yZXNpZGVudGRhdGFiYXNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e34470db1791c4961e8dc4b3d5eaf0920b8bfcf31c9ff95b6df0ca14d5d3ef4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16fa26674de41ed745e8b86018e0d1ff81b8155f41188f94286f429a562d9280JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e374335089cbbdc1b3bdfe7d2f42ea0832bf38e52b0770c709d7fdb720c1d771JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba86162aa56bb99b59e1d200e43427a8e78a472fc520663d1ad3200e72725631JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a1c37f5d32e62286e18070f0445d5e6c92ea42a898792569c2979c4dd0581f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9adb79e87f19292ed82c8dccdcaee7a7485f79fa0511ab69cc5232e89f137e2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ3IyeGRUWXJZLVEwMlBWZWJyVGRnaVE&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -628,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -662,19 +668,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,19 +688,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -702,19 +708,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -722,19 +728,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -742,19 +748,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -762,19 +768,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -782,19 +788,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -802,19 +808,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -822,19 +828,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -842,19 +848,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -862,19 +868,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -882,19 +888,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -902,19 +908,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -922,19 +928,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -942,19 +948,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -962,19 +968,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -982,19 +988,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1002,19 +1008,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1022,19 +1028,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1042,19 +1048,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1062,19 +1068,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,19 +1088,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1102,19 +1108,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1122,19 +1128,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1142,19 +1148,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1162,19 +1168,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1182,19 +1188,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1202,19 +1208,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1222,19 +1228,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1242,19 +1248,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1262,19 +1268,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1282,19 +1288,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1302,19 +1308,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1322,19 +1328,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1342,19 +1348,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1362,19 +1368,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1382,19 +1388,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1402,19 +1408,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1422,19 +1428,39 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" t="s">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
         <v>47</v>
       </c>
-      <c r="C40" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" t="s">
-        <v>88</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>89</v>
+      </c>
+      <c r="G41" t="s">
+        <v>90</v>
+      </c>
+      <c r="H41" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1478,6 +1504,7 @@
     <hyperlink ref="F38" r:id="rId37"/>
     <hyperlink ref="F39" r:id="rId38"/>
     <hyperlink ref="F40" r:id="rId39"/>
+    <hyperlink ref="F41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -40,39 +40,42 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Community Information-West Bloomfield Township,Michigan</t>
-  </si>
-  <si>
-    <t>Official Website ofWest Bloomfield Township,MI</t>
+    <t>Community- City ofColumbus,Ohio</t>
+  </si>
+  <si>
+    <t>CRISOhio</t>
+  </si>
+  <si>
+    <t>Home |Columbus State Community College</t>
   </si>
   <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
+    <t>Facilities &amp; Venues - City ofColumbus,Ohio</t>
+  </si>
+  <si>
+    <t>CommunityCenters -Columbus Recreation and Parks Department</t>
+  </si>
+  <si>
+    <t>Community resources in Columbus</t>
+  </si>
+  <si>
+    <t>IMPACTCommunityAction</t>
+  </si>
+  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home - Bloomfield Township</t>
-  </si>
-  <si>
-    <t>West Bloomfield Twp,MI- Facebook</t>
-  </si>
-  <si>
-    <t>Home - WB Parks</t>
-  </si>
-  <si>
-    <t>West Bloomfield Township,Michigan-Wikipedia</t>
-  </si>
-  <si>
-    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
-  </si>
-  <si>
-    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
+    <t>Home - GreaterColumbus CommunityHouse</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
   </si>
   <si>
+    <t>CivicFederal Credit Union</t>
+  </si>
+  <si>
     <t>Honda Civic- Wikipedia</t>
   </si>
   <si>
@@ -82,22 +85,19 @@
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
-    <t>Honda Civic For Sale- Carsforsale.com®</t>
+    <t>Used HondaCivicfor Sale inSterling,VA- CARFAX</t>
   </si>
   <si>
     <t>HondaCivic(eleventh generation) - Wikipedia</t>
   </si>
   <si>
-    <t>2026Honda CivicPrice, Reviews, Pictures &amp; More | Kelley Blue Book</t>
-  </si>
-  <si>
-    <t>2026Honda CivicReview, Pricing, &amp; Pictures | U.S. News</t>
-  </si>
-  <si>
-    <t>Honda Civic: Prices, Specs &amp; Features by Year | Cars.com</t>
-  </si>
-  <si>
-    <t>Used HondaCivicfor Sale Near Me - Autotrader</t>
+    <t>2026 HondaCivicFor Sale inSterling,VA- AutoNation Honda Dulles</t>
+  </si>
+  <si>
+    <t>Used HondaCivicfor Sale nearSterling,VA- CarGurus</t>
+  </si>
+  <si>
+    <t>Used HondaCivicnear me for sale</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -106,58 +106,58 @@
     <t>Neighbourhood-Wikipedia</t>
   </si>
   <si>
+    <t>TheNeighbourhood- Wourld Tour</t>
+  </si>
+  <si>
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
-    <t>TheNeighbourhood- Wourld Tour</t>
+    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>NEIGHBOURHOOD| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>The Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>The Neighbourhood-YouTube</t>
+    <t>neighborhood | inline online reservations</t>
+  </si>
+  <si>
+    <t>NEIGHBORHOOD</t>
   </si>
   <si>
     <t>Nextdoor - Discover yourneighbourhood</t>
   </si>
   <si>
-    <t>TheNeighbourhood- Sweater Weather (Official Video)</t>
-  </si>
-  <si>
-    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
+    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
   </si>
   <si>
     <t>The Residents Official Site</t>
   </si>
   <si>
-    <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
-  </si>
-  <si>
     <t>The Residents-Wikipedia</t>
   </si>
   <si>
-    <t>MichiganResidentsDatabase Search</t>
-  </si>
-  <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
     <t>Live &amp; Preserved - TheResidents</t>
   </si>
   <si>
+    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
+  </si>
+  <si>
     <t>RESIDENT| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>RESIDENT| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
-  </si>
-  <si>
-    <t>The Residents - Topic-YouTube</t>
+    <t>ResidentsCafé &amp; Bar | Michelin Bib Gourmand, Dupont Circle DC</t>
+  </si>
+  <si>
+    <t>The Residents-Facebook</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -166,124 +166,124 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54de27898d7c1ba5940c6f87e5ad4cbdc6e17f6f15c0ee036334f28c1d67bf70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcd92ac1d627d1a63b14f3bda4bb71844a8a09d079448396f789717972ba881bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=650b00e0574f97ade896fa9dd9e508c75313dfc5629d4b9ee9213ed2e3473cc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c232f2dcf3280844b048e397fb3811b69ca9c0b962eb0f1c1fa3ba5003c4bf91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=847240b31e4920bfdde1da6f5c721a193a4b1fd6793ca0c9b648eedfa8a31a66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffc9520a5d714d96bea6edb519b81246ceecad6c74bd261851f1f1d458a1105cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c64254109421b7a648c17044335ff440a5e9767c28d4b96d5d430b4192075c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a097f728640d1def226fc66c5345ea1299c0b97faae35fe2076f311c39b07fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ca214dcbd3aa77185f1c46f147437001b2ff1b87eea7dfefc2a65707fbba8c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48e631c30594c17a3e09d330ddf4227295ee251865538ddb082cf29f6abc467fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0345b7e1-2f35-6067-1a6f-a0002ee1617b&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064fcd156d7752a04be961544e964cd63b5062afbc14ade988a4333ca9b1f93cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6274d1c2b98278f0b26e0a0cc6ef21a467544ae78da13c2b3778d578376b3befJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5871783d9f8399a215c1a1201e06b64988e7d897c4b1b34f22f1a918037c4e0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d12df48da38a088b961cd0096bc5ef8d94c78b04308d99f97d23bff69425deeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a074658a0682f184c80899c5de24834ab8e85ab3a6d2a1d5c6319931ac0fb17aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=671810ee72e14fa5a314ed25f37863b331865c4e10731a10d55e09eba534fc86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=594aa24e660fd6c9c7f0689a5cb4ba074bbd069217eeea1a56a699cd13a9fbfcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cua2JiLmNvbS9ob25kYS9jaXZpYy8_bXNvY2tpZD0yOTNkYmNjMDA1Yzg2ZDczMDdlOGFiMjEwNGI1NmM3YQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5fdbef7acac471ac2cbedc4e3f9d91c51eb82613014e377b9f96518d43a10baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly9jYXJzLnVzbmV3cy5jb20vY2Fycy10cnVja3MvaG9uZGEvY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f8ca1646bf6dfbe4da1f53cbda24310f28ad26bf06678a227f5bc2db36492e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuY2Fycy5jb20vcmVzZWFyY2gvaG9uZGEtY2l2aWMvP21zb2NraWQ9MjkzZGJjYzAwNWM4NmQ3MzA3ZThhYjIxMDRiNTZjN2E&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a2f1ecff59fd0e4fdff53a6975392105b4624887f881e391bfcd00e96fa87a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=293dbcc0-05c8-6d73-07e8-ab2104b56c7a&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYz9tc29ja2lkPTI5M2RiY2MwMDVjODZkNzMwN2U4YWIyMTA0YjU2Yzdh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c86df2d4dc05fd8aa4cbb8f99e01dd04fef8110086e45b8b3cb38d258fb70c3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acc385d5646e30e6752794a3a0c416626596c2a4dff2b5c30d6770b179f282fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=578979cf0df6927a7c4b5b7675c91c7b2846648809673569000202e1542cd566JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4b67920829c31e4301677906818e0c24920effff023b1e1b2d8e7db3b353b84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71959afe0cd5b3198a37de9feed66eb949e0399c132d9272b8747eb27929909fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=134c5ed019cd7b7d8fdb62ff06eaf9eb2cbc74db6d2f170b256db07559d61ebbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9063a946e703fb09a93abca33897b1413a15c9b45bf82d9c94d4677299914c23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de3dd808b99a2319629bab57bd8d8ccee22ee766f44049f20d9b865de376c4ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9R0Nkd0toVHROTnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f775b402cc6925c9bab21840a1cb2d17d9fcb5ce2a58bcd2355f33467bf1983JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3e794ed2049b3bea980a2a5c14d6608b92a56110a499860c541637bec5f14bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28bd2d68-a5fb-6357-280f-3a89a4ba6296&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c520720b7d7d588357ce3457b32c6dadd150feb16a9c53c5aa58f7543e60c9f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbef615717c29aafa98ea5755980de770852cd3a8f0c811095a09d9ff08ae762JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MjRjZjExODVlZjE0Njc3ODNlZTIwNjY0ZWUwMzY2YmI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22c5042eba755dcb9df244dd8ed2aad45e6741e29f311a06924a4228ac907e79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=054abb13ba9b66fd53e4fb3b1f9f76021816937f99cf0d7bc01d073e678dfc01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cubWljaGlnYW5yZXNpZGVudGRhdGFiYXNlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e34470db1791c4961e8dc4b3d5eaf0920b8bfcf31c9ff95b6df0ca14d5d3ef4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16fa26674de41ed745e8b86018e0d1ff81b8155f41188f94286f429a562d9280JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e374335089cbbdc1b3bdfe7d2f42ea0832bf38e52b0770c709d7fdb720c1d771JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba86162aa56bb99b59e1d200e43427a8e78a472fc520663d1ad3200e72725631JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a1c37f5d32e62286e18070f0445d5e6c92ea42a898792569c2979c4dd0581f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9adb79e87f19292ed82c8dccdcaee7a7485f79fa0511ab69cc5232e89f137e2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cf1185-ef14-6778-3ee2-0664ee0366bb&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ3IyeGRUWXJZLVEwMlBWZWJyVGRnaVE&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94ff4bbe4b42331c58c7cf34b27f36dd41377874e1e4a3557dbcdb4da8815a3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=247003c261a7cb72a1a4cfbf5c00ba5404f02662142c73fb925f513d27e4ee64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY3Jpc29oaW8ub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd2575b02a14038bbf6be0690c77a854f4e93920eaa5c4ab4c1643e03b084e6fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY3NjYy5lZHUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74c21aa081a58f837d112a3eef00b37056dba7b5a7f361a1afa95673b8d07de7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8dc9fad29bce7a132a8be50fee1c60cf43ef62a7caa020e8aa8f24093a324fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eS9GYWNpbGl0aWVzLVZlbnVlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f44a951962a1595b2f3d6c7a7392e4baf1d9e06bd6f94940f0994e6cd33765ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9jb2x1bWJ1c3JlY3BhcmtzLmNvbS9mYWNpbGl0aWVzL2NvbW11bml0eWNlbnRlcnMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87c347be2a5713574945aeb73802b3323b1bfc5c3d7cb54511b175b18b8674ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXNvbnRoZWNoZWFwLmNvbS9yZXNvdXJjZXMtaW4tY29sdW1idXMtb2gv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32c1cb89b345141d6fc5da3fcff474d5b9c8763c884eb942132135176426a3bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuaW1wYWN0Y2Eub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba90f3195b712fa5aa598b4b0512c851533099e4baa046e26cac6bad0fe26525JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=662f65f7739d67eb771951c948eb8dcce1b4f10137693bca56c67f0db905a12aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9ncmVhdGVyY29sdW1idXNjaC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4fcebf30dd7b061ca40a7388a783ddb52ca8f2d0eb1f64aee86729105357de96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8ed02033faefbcbd43dc1b278b28d5131d33378da78bf79dec1a9c86381a42aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2l2aWNmY3Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38dfb04a85f1c5d544167bdae0837eccfe9475530399a9a7e02974bc8fec8afbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ce272c56a102006f20b88e06445a4b412dec16517bb7643006bb26907c705e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a396ad42bdea650b8d55a0b43b1bd1a86fdecbc7ee484d39fd9b0f9e2c2b877bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07729ea15eff4f5e5775b84e8631fa1d0e0dbf28ff766c55ce725dcde5916f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyZmF4LmNvbS9Vc2VkLUhvbmRhLUNpdmljLVN0ZXJsaW5nLVZBX3czMDNfYzE4NzM2P21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae779e6905089e0014df6c5c7e0d4722f756ad8892bb68eb53ccb7894811768bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e4153849ae97a2190efb28eb9a57981b4e9cdea9f64e11170f32982b5dae9d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuYXV0b25hdGlvbmhvbmRhZHVsbGVzLmNvbS9pbnZlbnRvcnkvYWxsLzIwMjYtaG9uZGEtY2l2aWMuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6886f42fbe6c778b0ae831ccf13333d4a1d87d06e194af22827498385b7c0b99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLVN0ZXJsaW5nLWQ1ODZfTDM2NTQ3P21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45c25fe3b5ef2759d4a7f95629287bdd760066f1d7921cfad85746a306da5699JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FybWF4LmNvbS9jYXJzL2hvbmRhL2NpdmljP21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ac4be10753af4a64717c454aa7eee27af26d21f8d067cc501203f55278ad430JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=126aac8403f74c59f834f231609a6047ddc0d48f560dd1c7a9a5b36ef5e35ce7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7efd23c561c862eb0defc77e543858e21cb737ba1b8bafad4b2f070799ef49e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0684dae0425d5f7443b26387ac05e86b3f68554a6d9308b1fb7815b8ff7c3e87JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d24b8dcd6ae6326b92e8ee716ca43c718635498231cbfaa04a445696ce9a3a8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=890cf340c80747aa837330bfdcfbab3493ee49b3378682ec14d53883b6bf2abfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL25laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=442df9fd585983bb812aba1ed7590da2af6a28ffe24afacb4288a165ffd2279cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07b8331467fe399885d862e8d3f46345a7ec16590bc69407cd7fb04b77d782e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9pbmxpbmUuYXBwL2Jvb2tpbmcvLU8wbWNaYXU5alFiX1FsQnFhRlclM0FpbmxpbmUtbGl2ZS0zLy1PMG1jWnZUREZvY1c5QnFLY2k4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=412aacd13cddfd47e44caf62c44566c767b16802e87d7105c522358564e98fb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly93d3cubmVpZ2hib3Job29kLmpwL2Vu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebf927242997699dd6e3cff473c5d4a44b6af9f9c27ab8a63c0e7862c24d8ec6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d906ffe6044284fa2db81940f88305154bf4ef7e19806ed39678d746c1e57238JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MTA4NzQwNzEzNDc3NjRiNTI2NGQ1NzkwMzU2MTY1YTk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=960d40321ca5f0d7f02b03a6cb382e4d16a695916d39a2523aaf7e7afbcf722cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0253e26fa8ddc4f9134ce1d652b9a89df98bba1e7e8e7b8bf5026dffc2ed433JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8db3836fe88f963270b60c037e1b9d29485f4d5d7c89d1bdfc6500fc4032b3e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=633da9cb2b8a17c842edeeb6ce17a935a3ac62b16b42d8b5bda7dcd8adc14ad3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=825435d47424356137bafdea11e89209010dcb5e60a096950f29691fbade9df9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34b68f1ebad9cd912c505693e825ec4f9a96b25ccdb5f3f755526fcf18d7e1acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ec4a8ca39351152bcc37f6cc9471e28a4bec55f7aa082e7f4cecfd5bf2b7f0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97a72bb19138a22b6da969cc17163e75105bc39812e45e6c15cc0cac290ccc4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzZGMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4b37c8fb1fc0051e371ba85e854c247736c2b631dc2fc1b612a4c804f016fabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL1RoZU9mZmljaWFsUmVzaWRlbnRzLw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="90">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,42 +40,39 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Community- City ofColumbus,Ohio</t>
-  </si>
-  <si>
-    <t>CRISOhio</t>
-  </si>
-  <si>
-    <t>Home |Columbus State Community College</t>
-  </si>
-  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>Facilities &amp; Venues - City ofColumbus,Ohio</t>
-  </si>
-  <si>
-    <t>CommunityCenters -Columbus Recreation and Parks Department</t>
-  </si>
-  <si>
-    <t>Community resources in Columbus</t>
-  </si>
-  <si>
-    <t>IMPACTCommunityAction</t>
+    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+  </si>
+  <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | 211LA</t>
+  </si>
+  <si>
+    <t>California Community Foundation| A Good Life for All</t>
   </si>
   <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home - GreaterColumbus CommunityHouse</t>
+    <t>Community(TV Series 2009–2015) - IMDb</t>
+  </si>
+  <si>
+    <t>Community– Parks &amp; Recreation</t>
+  </si>
+  <si>
+    <t>Homepage |LACCD</t>
+  </si>
+  <si>
+    <t>Home | Neighborhood Info</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
   </si>
   <si>
-    <t>CivicFederal Credit Union</t>
-  </si>
-  <si>
     <t>Honda Civic- Wikipedia</t>
   </si>
   <si>
@@ -85,19 +82,22 @@
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
-    <t>Used HondaCivicfor Sale inSterling,VA- CARFAX</t>
-  </si>
-  <si>
-    <t>HondaCivic(eleventh generation) - Wikipedia</t>
-  </si>
-  <si>
-    <t>2026 HondaCivicFor Sale inSterling,VA- AutoNation Honda Dulles</t>
-  </si>
-  <si>
-    <t>Used HondaCivicfor Sale nearSterling,VA- CarGurus</t>
-  </si>
-  <si>
-    <t>Used HondaCivicnear me for sale</t>
+    <t>New &amp; Used HondaCivicNearBrea,CA- Hardin Honda</t>
+  </si>
+  <si>
+    <t>Facilities•Civic&amp; Cultural Center -Brea,CA</t>
+  </si>
+  <si>
+    <t>Used Honda Civicfor Sale nearBrea,CA- CarGurus</t>
+  </si>
+  <si>
+    <t>Honda Dealer ServingBrea,CA- Sales, Service, Specials, Parts ...</t>
+  </si>
+  <si>
+    <t>Honda Civic For Sale- Carsforsale.com®</t>
+  </si>
+  <si>
+    <t>Used HondaCivicfor Sale Near Me inBrea,CA- Autotrader</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -106,58 +106,55 @@
     <t>Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>TheNeighbourhood- Wourld Tour</t>
-  </si>
-  <si>
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
-    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>NEIGHBOURHOOD| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>The Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>neighborhood | inline online reservations</t>
-  </si>
-  <si>
-    <t>NEIGHBORHOOD</t>
-  </si>
-  <si>
-    <t>Nextdoor - Discover yourneighbourhood</t>
+    <t>TheNeighbourhood- 2026 Tour Dates &amp; Concert Schedule - Live Nation</t>
+  </si>
+  <si>
+    <t>The Neighbourhood-YouTube</t>
+  </si>
+  <si>
+    <t>The NeighbourhoodTickets, Tour Dates &amp; Concerts 2027 &amp; 2026 -Songkick</t>
+  </si>
+  <si>
+    <t>The Neighbourhood Tickets&amp; 2026 Tour Dates |Vivid Seats</t>
+  </si>
+  <si>
+    <t>The Neighbourhood Tickets, 2026-2027 Concert Tour Dates</t>
   </si>
   <si>
     <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
   </si>
   <si>
+    <t>The Residents-Wikipedia</t>
+  </si>
+  <si>
     <t>The Residents Official Site</t>
   </si>
   <si>
-    <t>The Residents-Wikipedia</t>
-  </si>
-  <si>
     <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
     <t>Live &amp; Preserved - TheResidents</t>
   </si>
   <si>
+    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
-    <t>RESIDENT| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>ResidentsCafé &amp; Bar | Michelin Bib Gourmand, Dupont Circle DC</t>
-  </si>
-  <si>
-    <t>The Residents-Facebook</t>
+    <t>The Resident (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Free Reverse Address Lookup - TruePeopleSearch</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -166,124 +163,121 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94ff4bbe4b42331c58c7cf34b27f36dd41377874e1e4a3557dbcdb4da8815a3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=247003c261a7cb72a1a4cfbf5c00ba5404f02662142c73fb925f513d27e4ee64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY3Jpc29oaW8ub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd2575b02a14038bbf6be0690c77a854f4e93920eaa5c4ab4c1643e03b084e6fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY3NjYy5lZHUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74c21aa081a58f837d112a3eef00b37056dba7b5a7f361a1afa95673b8d07de7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8dc9fad29bce7a132a8be50fee1c60cf43ef62a7caa020e8aa8f24093a324fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eS9GYWNpbGl0aWVzLVZlbnVlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f44a951962a1595b2f3d6c7a7392e4baf1d9e06bd6f94940f0994e6cd33765ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9jb2x1bWJ1c3JlY3BhcmtzLmNvbS9mYWNpbGl0aWVzL2NvbW11bml0eWNlbnRlcnMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87c347be2a5713574945aeb73802b3323b1bfc5c3d7cb54511b175b18b8674ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXNvbnRoZWNoZWFwLmNvbS9yZXNvdXJjZXMtaW4tY29sdW1idXMtb2gv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32c1cb89b345141d6fc5da3fcff474d5b9c8763c884eb942132135176426a3bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cuaW1wYWN0Y2Eub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba90f3195b712fa5aa598b4b0512c851533099e4baa046e26cac6bad0fe26525JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=662f65f7739d67eb771951c948eb8dcce1b4f10137693bca56c67f0db905a12aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cc0ed7f-b717-66f4-3524-fa9eb6e86782&amp;u=a1aHR0cHM6Ly9ncmVhdGVyY29sdW1idXNjaC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4fcebf30dd7b061ca40a7388a783ddb52ca8f2d0eb1f64aee86729105357de96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8ed02033faefbcbd43dc1b278b28d5131d33378da78bf79dec1a9c86381a42aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2l2aWNmY3Uub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38dfb04a85f1c5d544167bdae0837eccfe9475530399a9a7e02974bc8fec8afbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ce272c56a102006f20b88e06445a4b412dec16517bb7643006bb26907c705e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a396ad42bdea650b8d55a0b43b1bd1a86fdecbc7ee484d39fd9b0f9e2c2b877bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07729ea15eff4f5e5775b84e8631fa1d0e0dbf28ff766c55ce725dcde5916f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyZmF4LmNvbS9Vc2VkLUhvbmRhLUNpdmljLVN0ZXJsaW5nLVZBX3czMDNfYzE4NzM2P21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae779e6905089e0014df6c5c7e0d4722f756ad8892bb68eb53ccb7894811768bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpY18oZWxldmVudGhfZ2VuZXJhdGlvbik&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e4153849ae97a2190efb28eb9a57981b4e9cdea9f64e11170f32982b5dae9d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuYXV0b25hdGlvbmhvbmRhZHVsbGVzLmNvbS9pbnZlbnRvcnkvYWxsLzIwMjYtaG9uZGEtY2l2aWMuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6886f42fbe6c778b0ae831ccf13333d4a1d87d06e194af22827498385b7c0b99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLVN0ZXJsaW5nLWQ1ODZfTDM2NTQ3P21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45c25fe3b5ef2759d4a7f95629287bdd760066f1d7921cfad85746a306da5699JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1114156d-8518-6513-37f6-028c84b16474&amp;u=a1aHR0cHM6Ly93d3cuY2FybWF4LmNvbS9jYXJzL2hvbmRhL2NpdmljP21zb2NraWQ9MTExNDE1NmQ4NTE4NjUxMzM3ZjYwMjhjODRiMTY0NzQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ac4be10753af4a64717c454aa7eee27af26d21f8d067cc501203f55278ad430JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=126aac8403f74c59f834f231609a6047ddc0d48f560dd1c7a9a5b36ef5e35ce7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7efd23c561c862eb0defc77e543858e21cb737ba1b8bafad4b2f070799ef49e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0684dae0425d5f7443b26387ac05e86b3f68554a6d9308b1fb7815b8ff7c3e87JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d24b8dcd6ae6326b92e8ee716ca43c718635498231cbfaa04a445696ce9a3a8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=890cf340c80747aa837330bfdcfbab3493ee49b3378682ec14d53883b6bf2abfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL25laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=442df9fd585983bb812aba1ed7590da2af6a28ffe24afacb4288a165ffd2279cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07b8331467fe399885d862e8d3f46345a7ec16590bc69407cd7fb04b77d782e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9pbmxpbmUuYXBwL2Jvb2tpbmcvLU8wbWNaYXU5alFiX1FsQnFhRlclM0FpbmxpbmUtbGl2ZS0zLy1PMG1jWnZUREZvY1c5QnFLY2k4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=412aacd13cddfd47e44caf62c44566c767b16802e87d7105c522358564e98fb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly93d3cubmVpZ2hib3Job29kLmpwL2Vu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebf927242997699dd6e3cff473c5d4a44b6af9f9c27ab8a63c0e7862c24d8ec6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=054cbad4-2d3e-637d-0ae9-ad352c736258&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d906ffe6044284fa2db81940f88305154bf4ef7e19806ed39678d746c1e57238JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MTA4NzQwNzEzNDc3NjRiNTI2NGQ1NzkwMzU2MTY1YTk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=960d40321ca5f0d7f02b03a6cb382e4d16a695916d39a2523aaf7e7afbcf722cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0253e26fa8ddc4f9134ce1d652b9a89df98bba1e7e8e7b8bf5026dffc2ed433JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8db3836fe88f963270b60c037e1b9d29485f4d5d7c89d1bdfc6500fc4032b3e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=633da9cb2b8a17c842edeeb6ce17a935a3ac62b16b42d8b5bda7dcd8adc14ad3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=825435d47424356137bafdea11e89209010dcb5e60a096950f29691fbade9df9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34b68f1ebad9cd912c505693e825ec4f9a96b25ccdb5f3f755526fcf18d7e1acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ec4a8ca39351152bcc37f6cc9471e28a4bec55f7aa082e7f4cecfd5bf2b7f0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97a72bb19138a22b6da969cc17163e75105bc39812e45e6c15cc0cac290ccc4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzZGMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4b37c8fb1fc0051e371ba85e854c247736c2b631dc2fc1b612a4c804f016fabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10874071-3477-64b5-264d-5790356165a9&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL1RoZU9mZmljaWFsUmVzaWRlbnRzLw&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ba2d151c6e4b546b99666365b72cce8557b8dd1b5bc0fca37b6c54b18ae51f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f053d0e3e6283e1030a817b44fc591d52fa46469e79330ac706b24d27c86865cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce15d2c4d278cc358c6e7ae437be6e80d6277842420aa8633591aeca61ce45e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a10ff5a01ab1af678c09cc28e03accbc38a6b2001e2541879bc5fecf8d57a3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cdb0ddf71cb4a3dca070176f3a9246863e7da87f7aceb1fdfe91bb03369a04cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81096ec163c41e1c4f33a5f935f60e285da04c590eb2ac47b871681d7591fd23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa768056903a50561b59410ea4aa4cac51645781d67e7fc1caa97c00b8c07e12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa88d796d980703bdac2e8b2195f32abe1f8a3024fed3a2957944bda47d8e840JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d68036342e6bc81c05dd31c3ff3228fd15d0213b7ab38a29036b3babb29d419JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24befbb7e4e74c99e45b6bb4d2c9493ac4c8b5497720ec5cffc6841994fe0a5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b85ade1e30332dbf39913384e81f8d68f80ea5877c4029e9cfe599ab4a36f251JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c1d2b6bdbe36c614c6da563fc39646cb799d1c7da868e4feb22292d6a19e479JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4014e698605cab8c217236c19026d7ebd9a1f696fdd9a5c9eb7e25d200c84a04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ee244a085e6bb7ed310a86956191f6ef22013b6b0b0115a02c0a0ea22d5d8a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d13b17c39e6a3643b0bfa45a48ce714406e946bf7d9b2041731f59693296c232JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2d40fda086163abf39338cf63f89bc0c1c4557de467093f0132333b7bc3f965JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e17d9cb51a8cd22d0bfdddb38a20d645a933a53cd4ddbc4eb453091b96f61036JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTAyNmM5NzBmNmJhZDYyYTMzOGU3ODBlZTZhY2I2M2Y1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ebe2f64bbac34f54533f4f9999b9cd58e72c56f2b5845a0273d72d5e447d302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce65ed84c71b2023bf067743b025a116dbcf475c217a502db967f00462dc4a81JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87763522dc40ee2ad7d110e834f3963eda51e0d37d0f32563ffc394a5c4afffaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9MDI2Yzk3MGY2YmFkNjJhMzM4ZTc4MGVlNmFjYjYzZjU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a604d5b9f293d3465efb9c0ba549b9bb5f95e7b8a19948b3ce76d116f90de576JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7d48430d85054cde6cfed16def0a732f597e5a8978487db0e24ebd2c771e900JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=978df716e5683d57506736bb85239632aa565c040e1b4ead19c4b1f6970bfdd3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c54cb79191418ed8a7f216eaaa7a8e585f1cd1324fd05781a1fac64318ec8f70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6294c5ed2e7f30d5d60486c9d1ee36565ed3d07f78e39b5c6ca537be101aaee2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bf163167e653d5c95c0dafff3b43a0fa25b1c11538c0a64ad883c8556a1fabbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=030919246289a3a6d6e16543ff57f151d40ac006b80e9776b6fc3fdd44e22d47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8aae8b55ec918eff5d30df985eb81d64bafb5b8ea40a3073ef460f5ab4295a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0yZjBkZjlkMDY5MmQ2MTU2MjE1NWVlMzE2OGM4NjBjMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d1c6f2de0818a1153fd47d825ff977b50588b2a0bf753bb514bd395aa750f5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MmYwZGY5ZDA2OTJkNjE1NjIxNTVlZTMxNjhjODYwYzE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea4667aa79c89a9e4cf4ae796b9918e6a24dc9fd259b2940200df3ab2577e69cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9M2M2OWY4Y2UyZmViNjJiYjE4NzFlZjJmMmVhNTYzOWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fecf57cd2c10e25843698243e6227c392b41236160a72d3a6a50e68780d314edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d63e942e0d9fdf7d478f3fb4b5d73ec29978c78bab59eaa45b39dfcd1d4dd20eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73627b7fd974087f413c96038e10d97d162acec082d48bde3bf0fa167e1f03d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe5a12d3453b6f96dafec3a252081d9586838bc109276e256a7061cbb7d4ea1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=010eb83a3832701d8c2a08eacd28967f65aa25751968750d0a9f9e8357a44bc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=888f13f0c9002fdfe8c383f724c699870fd08e2f6b5c2c643839fdebf6be6ca8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8347e437741ce40a935041892d791d4e85ed8b1cb782332767f53bd87c7d9bd5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e1e880ff03ef79f25d56ea79eddf1588b9cf508b75484452ddd179f52679247JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32783f5aa49d2e0d97f34aef54bfa69802f0b6630b1d0090283a24e966f2d76bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -634,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -668,19 +662,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -688,19 +682,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -708,19 +702,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,19 +722,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -748,19 +742,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -768,19 +762,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -788,19 +782,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -808,19 +802,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -828,19 +822,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -848,19 +842,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -868,19 +862,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -888,19 +882,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -908,19 +902,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -928,19 +922,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -948,19 +942,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -968,19 +962,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -988,19 +982,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1008,19 +1002,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1028,19 +1022,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1048,19 +1042,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1068,19 +1062,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1088,19 +1082,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1108,19 +1102,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1128,19 +1122,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1148,19 +1142,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1168,19 +1162,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1188,19 +1182,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1208,19 +1202,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1228,19 +1222,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1248,19 +1242,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1268,19 +1262,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1288,19 +1282,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1308,19 +1302,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1328,19 +1322,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1348,19 +1342,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1368,19 +1362,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1388,19 +1382,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1408,19 +1402,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1428,39 +1422,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41" t="s">
-        <v>90</v>
-      </c>
-      <c r="H41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1478,6 @@
     <hyperlink ref="F38" r:id="rId37"/>
     <hyperlink ref="F39" r:id="rId38"/>
     <hyperlink ref="F40" r:id="rId39"/>
-    <hyperlink ref="F41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Community_Development.xlsx
+++ b/results/scraped_Cape_Town_Community_Development.xlsx
@@ -43,61 +43,61 @@
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+    <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>City ofSt. Petersburg</t>
   </si>
   <si>
     <t>Community (TV series) -Wikipedia</t>
   </si>
   <si>
-    <t>Home | 211LA</t>
-  </si>
-  <si>
-    <t>California Community Foundation| A Good Life for All</t>
-  </si>
-  <si>
-    <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
+    <t>LGBTQ+Community-St. Petersburg, Florida</t>
   </si>
   <si>
     <t>Community(TV Series 2009–2015) - IMDb</t>
   </si>
   <si>
-    <t>Community– Parks &amp; Recreation</t>
-  </si>
-  <si>
-    <t>Homepage |LACCD</t>
-  </si>
-  <si>
-    <t>Home | Neighborhood Info</t>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
+  </si>
+  <si>
+    <t>55+CommunityHomes for Sale in Saint PetersburgFL- Zillow</t>
+  </si>
+  <si>
+    <t>55Plus Community - Saint Petersburg FLReal Estate -Zillow</t>
+  </si>
+  <si>
+    <t>A 55+CommunityinSt. Petersburg,Florida- Harbor Lights</t>
   </si>
   <si>
     <t>Honda CivicFamily: Models &amp; Price | Honda</t>
   </si>
   <si>
+    <t>CivicFederal Credit Union</t>
+  </si>
+  <si>
+    <t>LaramiePlainsCivicCenter</t>
+  </si>
+  <si>
     <t>Honda Civic- Wikipedia</t>
   </si>
   <si>
     <t>2026CivicSedan - Fun &amp; Sporty Compact w/ Hybrid Option</t>
   </si>
   <si>
+    <t>Used Honda Civic for SalenearLaramie,WY- CarGurus</t>
+  </si>
+  <si>
+    <t>New HondaCivicfor Sale inLaramie,WY| Edmunds</t>
+  </si>
+  <si>
+    <t>Used Honda Civic for Sale in Laramie,WY| Edmunds</t>
+  </si>
+  <si>
     <t>2026Honda CivicReview, Pricing, and Specs - Car and Driver</t>
   </si>
   <si>
-    <t>New &amp; Used HondaCivicNearBrea,CA- Hardin Honda</t>
-  </si>
-  <si>
-    <t>Facilities•Civic&amp; Cultural Center -Brea,CA</t>
-  </si>
-  <si>
-    <t>Used Honda Civicfor Sale nearBrea,CA- CarGurus</t>
-  </si>
-  <si>
-    <t>Honda Dealer ServingBrea,CA- Sales, Service, Specials, Parts ...</t>
-  </si>
-  <si>
-    <t>Honda Civic For Sale- Carsforsale.com®</t>
-  </si>
-  <si>
-    <t>Used HondaCivicfor Sale Near Me inBrea,CA- Autotrader</t>
+    <t>Used HondaCivicfor Sale inLaramie,WY(with Photos) - TRUECar</t>
   </si>
   <si>
     <t>Nextdoor</t>
@@ -106,55 +106,55 @@
     <t>Neighbourhood-Wikipedia</t>
   </si>
   <si>
+    <t>TheNeighbourhood- Wourld Tour</t>
+  </si>
+  <si>
     <t>Join your neighborhood |Nextdoor</t>
   </si>
   <si>
     <t>The Neighbourhood-Wikipedia</t>
   </si>
   <si>
-    <t>TheNeighbourhood- 2026 Tour Dates &amp; Concert Schedule - Live Nation</t>
-  </si>
-  <si>
-    <t>The Neighbourhood-YouTube</t>
-  </si>
-  <si>
-    <t>The NeighbourhoodTickets, Tour Dates &amp; Concerts 2027 &amp; 2026 -Songkick</t>
-  </si>
-  <si>
-    <t>The Neighbourhood Tickets&amp; 2026 Tour Dates |Vivid Seats</t>
-  </si>
-  <si>
-    <t>The Neighbourhood Tickets, 2026-2027 Concert Tour Dates</t>
+    <t>Nextdoor - Discover yourneighbourhood</t>
+  </si>
+  <si>
+    <t>Neighbourhood| Definition &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>Login - Nextdoor</t>
+  </si>
+  <si>
+    <t>TheNeighbourhood– Official Biography, Songs, Albums &amp; Tour Dates</t>
   </si>
   <si>
     <t>Residence vs.Residents: What's the Difference? - Grammarly</t>
   </si>
   <si>
+    <t>The Residents Official Site</t>
+  </si>
+  <si>
+    <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
     <t>The Residents-Wikipedia</t>
   </si>
   <si>
-    <t>The Residents Official Site</t>
-  </si>
-  <si>
-    <t>RESIDENTDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
     <t>RESIDENT| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
+    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
+  </si>
+  <si>
     <t>Live &amp; Preserved - TheResidents</t>
   </si>
   <si>
-    <t>RESIDENT| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>RESIDENTSDefinition &amp; Meaning | Dictionary.com</t>
-  </si>
-  <si>
-    <t>The Resident (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Free Reverse Address Lookup - TruePeopleSearch</t>
+    <t>Residents- definition ofresidentsby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>Residentsvs. Residence - Which is Correct?</t>
   </si>
   <si>
     <t>Community Development</t>
@@ -163,121 +163,121 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ba2d151c6e4b546b99666365b72cce8557b8dd1b5bc0fca37b6c54b18ae51f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f053d0e3e6283e1030a817b44fc591d52fa46469e79330ac706b24d27c86865cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce15d2c4d278cc358c6e7ae437be6e80d6277842420aa8633591aeca61ce45e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a10ff5a01ab1af678c09cc28e03accbc38a6b2001e2541879bc5fecf8d57a3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cdb0ddf71cb4a3dca070176f3a9246863e7da87f7aceb1fdfe91bb03369a04cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81096ec163c41e1c4f33a5f935f60e285da04c590eb2ac47b871681d7591fd23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa768056903a50561b59410ea4aa4cac51645781d67e7fc1caa97c00b8c07e12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa88d796d980703bdac2e8b2195f32abe1f8a3024fed3a2957944bda47d8e840JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d68036342e6bc81c05dd31c3ff3228fd15d0213b7ab38a29036b3babb29d419JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24befbb7e4e74c99e45b6bb4d2c9493ac4c8b5497720ec5cffc6841994fe0a5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f58400b-28c5-6e60-29d4-57ea29036f9f&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b85ade1e30332dbf39913384e81f8d68f80ea5877c4029e9cfe599ab4a36f251JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c1d2b6bdbe36c614c6da563fc39646cb799d1c7da868e4feb22292d6a19e479JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9uZGFfQ2l2aWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4014e698605cab8c217236c19026d7ebd9a1f696fdd9a5c9eb7e25d200c84a04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ee244a085e6bb7ed310a86956191f6ef22013b6b0b0115a02c0a0ea22d5d8a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d13b17c39e6a3643b0bfa45a48ce714406e946bf7d9b2041731f59693296c232JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2NpdmljLWJyZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2d40fda086163abf39338cf63f89bc0c1c4557de467093f0132333b7bc3f965JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2l0eW9mYnJlYS5nb3YvRmFjaWxpdGllcy9GYWNpbGl0eS9EZXRhaWxzL0NpdmljLUN1bHR1cmFsLUNlbnRlci0zOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e17d9cb51a8cd22d0bfdddb38a20d645a933a53cd4ddbc4eb453091b96f61036JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUJyZWEtZDU4Nl9MMjUxOT9tc29ja2lkPTAyNmM5NzBmNmJhZDYyYTMzOGU3ODBlZTZhY2I2M2Y1&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ebe2f64bbac34f54533f4f9999b9cd58e72c56f2b5845a0273d72d5e447d302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuaGFyZGluaG9uZGEuY29tL2hvbmRhLWRlYWxlci1icmVhLWNhLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce65ed84c71b2023bf067743b025a116dbcf475c217a502db967f00462dc4a81JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuY2Fyc2ZvcnNhbGUuY29tL2hvbmRhLWNpdmljLWZvci1zYWxlLUM0NjI2MjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87763522dc40ee2ad7d110e834f3963eda51e0d37d0f32563ffc394a5c4afffaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=026c970f-6bad-62a3-38e7-80ee6acb63f5&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vY2Fycy1mb3Itc2FsZS9ob25kYS9jaXZpYy9icmVhLWNhP21zb2NraWQ9MDI2Yzk3MGY2YmFkNjJhMzM4ZTc4MGVlNmFjYjYzZjU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a604d5b9f293d3465efb9c0ba549b9bb5f95e7b8a19948b3ce76d116f90de576JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7d48430d85054cde6cfed16def0a732f597e5a8978487db0e24ebd2c771e900JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9OZWlnaGJvdXJob29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=978df716e5683d57506736bb85239632aa565c040e1b4ead19c4b1f6970bfdd3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c54cb79191418ed8a7f216eaaa7a8e585f1cd1324fd05781a1fac64318ec8f70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6294c5ed2e7f30d5d60486c9d1ee36565ed3d07f78e39b5c6ca537be101aaee2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTdLemVmL3RoZS1uZWlnaGJvdXJob29kLWV2ZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bf163167e653d5c95c0dafff3b43a0fa25b1c11538c0a64ad883c8556a1fabbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0RBWHVzWXdSSnBpU1AyQ0huWG5Wbnc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=030919246289a3a6d6e16543ff57f151d40ac006b80e9776b6fc3fdd44e22d47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cuc29uZ2tpY2suY29tL2FydGlzdHMvNjM2ODQ4LW5laWdoYm91cmhvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8aae8b55ec918eff5d30df985eb81d64bafb5b8ea40a3073ef460f5ab4295a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cudml2aWRzZWF0cy5jb20vdGhlLW5laWdoYm91cmhvb2QtdGlja2V0cy9wZXJmb3JtZXIvMzA5ODI_bXNvY2tpZD0yZjBkZjlkMDY5MmQ2MTU2MjE1NWVlMzE2OGM4NjBjMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d1c6f2de0818a1153fd47d825ff977b50588b2a0bf753bb514bd395aa750f5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0df9d0-692d-6156-2155-ee3168c860c1&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9UaGUtTmVpZ2hib3VyaG9vZC10aWNrZXRzL2FydGlzdC8yMTY0NzE4P21zb2NraWQ9MmYwZGY5ZDA2OTJkNjE1NjIxNTVlZTMxNjhjODYwYzE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea4667aa79c89a9e4cf4ae796b9918e6a24dc9fd259b2940200df3ab2577e69cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9M2M2OWY4Y2UyZmViNjJiYjE4NzFlZjJmMmVhNTYzOWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fecf57cd2c10e25843698243e6227c392b41236160a72d3a6a50e68780d314edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d63e942e0d9fdf7d478f3fb4b5d73ec29978c78bab59eaa45b39dfcd1d4dd20eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73627b7fd974087f413c96038e10d97d162acec082d48bde3bf0fa167e1f03d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe5a12d3453b6f96dafec3a252081d9586838bc109276e256a7061cbb7d4ea1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=010eb83a3832701d8c2a08eacd28967f65aa25751968750d0a9f9e8357a44bc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=888f13f0c9002fdfe8c383f724c699870fd08e2f6b5c2c643839fdebf6be6ca8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8347e437741ce40a935041892d791d4e85ed8b1cb782332767f53bd87c7d9bd5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e1e880ff03ef79f25d56ea79eddf1588b9cf508b75484452ddd179f52679247JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UaGVfUmVzaWRlbnRfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32783f5aa49d2e0d97f34aef54bfa69802f0b6630b1d0090283a24e966f2d76bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c69f8ce-2feb-62bb-1871-ef2f2ea5639d&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZXBlb3BsZXNlYXJjaC5jb20vYWRkcmVzcy1sb29rdXA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2443c71ab0d99c51e11ee775b7c38dd69830194c2bae87fbfd07b13f41a4b4edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebcc25cde8b3105339c0e22eabb940dbba33caf7716d9e650642352f980882d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77266e5db2e0ac4d2021b61653a024ce45a0ab07d7fdac694aab125772a46ca0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cuc3RwZXRlLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=601b8f1696fffbd592562caecd0dd5aedadd16ec5a5fb4b65012f08a18d25793JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53a484cadef0d0b341d738cb1f400496acec29436465b665846ad3421eec7fb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cuc3RwZXRlLm9yZy92aXNpdG9ycy9sZ2J0cV9jb21tdW5pdHkucGhw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e21c73cb94f449c75e4cbc5105ddb0a990fc236ff1f053a662440256ffabe03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNDM5NjI5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb6623f3a388167f864ae2fb67a2f9a3dea426c00957c9c52acd078f60e1b08aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=baff025e85e98dfda08e66e589457353921d97f3085a1cf308c1acc315ee47ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cuemlsbG93LmNvbS9zYWludC1wZXRlcnNidXJnLWZsLzU1LWNvbW11bml0eS8_bXNvY2tpZD0xODc0NDBiYWU5NGE2ODM3MzQ1ZjU3NWJlODdkNjlkNw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e8767cb663f55bd4832bba60aa1903436c4249606457728f310758a1f420e9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly93d3cuemlsbG93LmNvbS9zYWludC1wZXRlcnNidXJnLWZsLzU1cGx1cy1jb21tdW5pdHlfYXR0Lz9tc29ja2lkPTE4NzQ0MGJhZTk0YTY4MzczNDVmNTc1YmU4N2Q2OWQ3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3e3f6cd15f249976caa66394364e321dddf652d42d04974f4431b382647e0a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=187440ba-e94a-6837-345f-575be87d69d7&amp;u=a1aHR0cHM6Ly9oYXJib3JsaWdodHNjbHViLmNvbS9jb21tdW5pdHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cc790540dea724609c614cdcd5dabf9c5a3ef0703a941109886d6b817d11423JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb9642543214a2949fdbcfc028bce299de1309c8cb31bfc7b4d8bcc53f4d6082JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cuY2l2aWNmY3Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4911e8cc2966748e7347b14cd67a3ed505a634ebeee1f55cbeb94d064842d67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cDovL2xwY2N3eS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83729837f6a92f7a610ee85cde77be4a815aa77bfba3f32eb8ef851c87091c82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib25kYV9DaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32b63e515cc8118b0a515a46e75a2d5f12ea62a7151694a56e63ba905f018475JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly9hdXRvbW9iaWxlcy5ob25kYS5jb20vY2l2aWMtc2VkYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ec30160f8d20cdce8e5935d005682b8ee1eb6f2dea50bcc1365c190c15a310dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cuY2FyZ3VydXMuY29tL0NhcnMvbC1Vc2VkLUhvbmRhLUNpdmljLUxhcmFtaWUtZDU4Nl9MNDA0ODk_bXNvY2tpZD0wMzU0NTc1MTkxYmY2YzdhMzgxYTQwYjA5MGRlNmQ2Mw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fbb44dccf05b2d7fdafed17d9dde18f09d763fcb806d0d2c1267dd5580cdaed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cuZWRtdW5kcy5jb20vbmV3LWhvbmRhLWNpdmljLWZvci1zYWxlLWxhcmFtaWUtd3kvP21zb2NraWQ9MDM1NDU3NTE5MWJmNmM3YTM4MWE0MGIwOTBkZTZkNjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9baadd4fbde8203b24f67a782c33496afd47c0a560b5db4266456c9987a65debJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cuZWRtdW5kcy5jb20vdXNlZC1ob25kYS1jaXZpYy1sYXJhbWllLXd5Lz9tc29ja2lkPTAzNTQ1NzUxOTFiZjZjN2EzODFhNDBiMDkwZGU2ZDYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=627bd8aff9f93ef543d174de41638238d9ac1eae8f7f82220632b335f65172d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cuY2FyYW5kZHJpdmVyLmNvbS9ob25kYS9jaXZpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=882c059589f120d6c5ac3eb5cff52be933a1c257b8889b3eb467064aaf002985JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03545751-91bf-6c7a-381a-40b090de6d63&amp;u=a1aHR0cHM6Ly93d3cudHJ1ZWNhci5jb20vdXNlZC1jYXJzLWZvci1zYWxlL2xpc3RpbmdzL2hvbmRhL2NpdmljL2xvY2F0aW9uLWxhcmFtaWUtd3kv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13146f935a10b89cd7e77f046375190d915704aad5b6499b8e03ff19088f4897JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=133a81917b44c6d2861ba97ba54dc607d81a37a922a7ee71c9bc27981cc4e354JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmVpZ2hib3VyaG9vZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=045a889698aa7f08d1f04ae448ba4facf9066936f612d57a09b0e4f404f9f929JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly90b3VyLnRoZW5iaGQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2eb5eee603dcb0f0f9246517132f1f27b3a3fd5b1c24af7a46de641d985c67acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9uZXh0ZG9vci5jb20vZmluZC1uZWlnaGJvcmhvb2Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4555004f7193f9fe59e1b01e6012c733f4cd06577bbb32d9e3708689c76dff75JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX05laWdoYm91cmhvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfb476277149ca77da4edfaeba2cf508bc400734aac8ed26b29d338a62507c5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdb24e5d3e08aad7999c0a513921b1d450f31dced2fe6ed48a956a599f55ec1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbmVpZ2hib3Job29kLXNvY2lvbG9neQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c188d4d5dcb0a8ee259b8f444c2c6486fb093594f540c533844888ac56523decJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly9jYS5uZXh0ZG9vci5jb20vbG9naW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b70eec8d4ef19cbb75ed4b5929e6347e8df718d5a5b64339f9ad6257d9c2bfeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123c6ae1-8910-68c6-2111-7d00880f691f&amp;u=a1aHR0cHM6Ly93d3cudGhlbmVpZ2hib3VyaG9vZC5uZXQvYmlv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6b9865117b3b8364f4a0c9cf65bab12639f6d8c8ca49a2ca2baf41fa8d4ef05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9jb21tb25seS1jb25mdXNlZC13b3Jkcy9yZXNpZGVuY2UtdnMtcmVzaWRlbnRzP21zb2NraWQ9MGQ0MjJmZDIzNjlmNjk1MDM4MTAzODMzMzdmZTY4OTA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18610f0108cc9b11c9501c048dbf243802e0f44eedfa2423c0ede03b31c94e1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c504d80817d0f7078c2d7532cad06a98635eb1904abdd6e45ab1be9333881e6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e863434891d04a0e4eb7c455defc9c59350dadd75d71ec231fd4550c378a05baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlX1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19266cedfdd9da1b80863de8ae4e289dfb2ad0a766d27abbacd2c6d47023e2dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d518e2d371d1d4d614172ec52682750ed5ccc657c3a3582f138d1ce08fd11a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Jlc2lkZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa952679a023868c5ae7c685c799b419f6692bb0297301710f619a041b0a785fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=927201269edc85077ac6a4356dc43039fb598c7de85def70fb99ca859c78ee17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cucmVzaWRlbnRzLmNvbS90b3VyZGF0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd6649b140324bfd4e85e9420a90cecc3dadfe6b2167bafd441345d87b6146fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL1Jlc2lkZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73611c9b07419dd3a753befbf9ad06d0495f7908cb664cd84c662c2c662486b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d422fd2-369f-6950-3810-383337fe6890&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vcmVzaWRlbnRzLXZzLXJlc2lkZW5jZS8&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
